--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12">

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC34">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q17">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q29">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q19">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-03 15:15:00</t>
+          <t>2026-08-03 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>13.2</v>
+        <v>2.81</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4755,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-03 15:30:00</t>
+          <t>2026-08-03 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="P28">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE28">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="O29">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>5.17</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-03 16:00:00</t>
+          <t>2026-08-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-03 21:00:00</t>
+          <t>2026-08-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5809,151 +5809,477 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FC Avan Academy</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Delfin SC</t>
         </is>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N34">
+      <c r="N36">
         <v>1.31</v>
       </c>
-      <c r="O34">
+      <c r="O36">
         <v>4.92</v>
       </c>
-      <c r="P34">
+      <c r="P36">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
         <v>1.9</v>
       </c>
-      <c r="AB34">
+      <c r="AB36">
         <v>1.78</v>
       </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>2026-08-03 21:00:00</t>
         </is>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>3.86</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13">

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1133,55 +1133,55 @@
         <v>10.9</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,31 +1809,31 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2461,31 +2461,31 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>2.32</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA15">
         <v>1.9</v>
@@ -2799,19 +2799,19 @@
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>1.33</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>7.47</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>2.07</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>3.07</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>8.6</v>
+        <v>1.37</v>
       </c>
       <c r="O21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P21">
-        <v>1.33</v>
+        <v>7.47</v>
       </c>
       <c r="Q21">
-        <v>6.36</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC21">
+        <v>2.13</v>
+      </c>
+      <c r="AD21">
+        <v>1.7</v>
+      </c>
+      <c r="AE21">
+        <v>1.28</v>
+      </c>
+      <c r="AF21">
+        <v>1.6</v>
+      </c>
+      <c r="AG21">
         <v>2.1</v>
       </c>
-      <c r="AD21">
-        <v>1.72</v>
-      </c>
-      <c r="AE21">
-        <v>1.29</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.07</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>2.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.37</v>
+        <v>8.6</v>
       </c>
       <c r="O22">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>7.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q22">
-        <v>1.83</v>
+        <v>6.36</v>
       </c>
       <c r="R22">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA22">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AC22">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD22">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.16</v>
+        <v>2.89</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -2600,55 +2600,55 @@
         <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>3.12</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>3.54</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>3.41</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>2.81</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,40 +4882,40 @@
         <v>13.2</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC28">
         <v>1.92</v>
@@ -4924,13 +4924,13 @@
         <v>1.8</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>5.17</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -6186,34 +6186,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AA36">
         <v>1.9</v>
@@ -6222,19 +6222,19 @@
         <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU36"/>
+  <dimension ref="A1:AU43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2135,31 +2135,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="R12">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,16 +2298,16 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB12">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
         <v>2.4</v>
@@ -2316,13 +2316,13 @@
         <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,22 +2437,22 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
+        <v>2.35</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>2.45</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2.18</v>
-      </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2461,31 +2461,31 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD13">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.37</v>
+        <v>8.6</v>
       </c>
       <c r="O21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>7.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>6.36</v>
       </c>
       <c r="R21">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AC21">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>2.89</v>
       </c>
       <c r="AK21">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>8.6</v>
+        <v>1.37</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P22">
-        <v>1.33</v>
+        <v>7.47</v>
       </c>
       <c r="Q22">
-        <v>6.36</v>
+        <v>1.83</v>
       </c>
       <c r="R22">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
+        <v>2.13</v>
+      </c>
+      <c r="AD22">
+        <v>1.7</v>
+      </c>
+      <c r="AE22">
+        <v>1.28</v>
+      </c>
+      <c r="AF22">
+        <v>1.6</v>
+      </c>
+      <c r="AG22">
         <v>2.1</v>
       </c>
-      <c r="AD22">
-        <v>1.72</v>
-      </c>
-      <c r="AE22">
-        <v>1.29</v>
-      </c>
-      <c r="AF22">
-        <v>1.57</v>
-      </c>
-      <c r="AG22">
-        <v>2.07</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-03 21:00:00</t>
+          <t>2026-08-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,151 +6135,1292 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Levski Sofia</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kairat</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kauno Žalgiris</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Delfin SC</t>
         </is>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N36">
+      <c r="N43">
         <v>1.31</v>
       </c>
-      <c r="O36">
+      <c r="O43">
         <v>4.92</v>
       </c>
-      <c r="P36">
+      <c r="P43">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q36">
+      <c r="Q43">
         <v>1.8</v>
       </c>
-      <c r="R36">
+      <c r="R43">
         <v>2.23</v>
       </c>
-      <c r="S36">
+      <c r="S43">
         <v>1.36</v>
       </c>
-      <c r="T36">
+      <c r="T43">
         <v>2.7</v>
       </c>
-      <c r="U36">
+      <c r="U43">
         <v>2.62</v>
       </c>
-      <c r="V36">
+      <c r="V43">
         <v>1.36</v>
       </c>
-      <c r="W36">
+      <c r="W43">
         <v>1.07</v>
       </c>
-      <c r="X36">
+      <c r="X43">
         <v>1.01</v>
       </c>
-      <c r="Y36">
+      <c r="Y43">
         <v>1.26</v>
       </c>
-      <c r="Z36">
+      <c r="Z43">
         <v>3.31</v>
       </c>
-      <c r="AA36">
+      <c r="AA43">
         <v>1.9</v>
       </c>
-      <c r="AB36">
+      <c r="AB43">
         <v>1.78</v>
       </c>
-      <c r="AC36">
+      <c r="AC43">
         <v>3.3</v>
       </c>
-      <c r="AD36">
+      <c r="AD43">
         <v>1.31</v>
       </c>
-      <c r="AE36">
+      <c r="AE43">
         <v>1.07</v>
       </c>
-      <c r="AF36">
+      <c r="AF43">
         <v>2.17</v>
       </c>
-      <c r="AG36">
+      <c r="AG43">
         <v>1.57</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.15</v>
       </c>
-      <c r="AK36">
+      <c r="AK43">
         <v>3.18</v>
       </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>2026-08-03 21:00:00</t>
         </is>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1133,22 +1133,22 @@
         <v>10.9</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
         <v>4</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
         <v>1.15</v>
@@ -1160,28 +1160,28 @@
         <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
         <v>1.43</v>
       </c>
       <c r="AB5">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC5">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD5">
         <v>1.71</v>
       </c>
       <c r="AE5">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK5">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,31 +1809,31 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2135,31 +2135,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q12">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2461,31 +2461,31 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.37</v>
+        <v>8.6</v>
       </c>
       <c r="O21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>7.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>6.36</v>
       </c>
       <c r="R21">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AC21">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>2.89</v>
       </c>
       <c r="AK21">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>8.6</v>
+        <v>1.37</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P22">
-        <v>1.33</v>
+        <v>7.47</v>
       </c>
       <c r="Q22">
-        <v>6.36</v>
+        <v>1.83</v>
       </c>
       <c r="R22">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
+        <v>2.13</v>
+      </c>
+      <c r="AD22">
+        <v>1.7</v>
+      </c>
+      <c r="AE22">
+        <v>1.28</v>
+      </c>
+      <c r="AF22">
+        <v>1.6</v>
+      </c>
+      <c r="AG22">
         <v>2.1</v>
       </c>
-      <c r="AD22">
-        <v>1.72</v>
-      </c>
-      <c r="AE22">
-        <v>1.29</v>
-      </c>
-      <c r="AF22">
-        <v>1.57</v>
-      </c>
-      <c r="AG22">
-        <v>2.07</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G38">
@@ -6512,55 +6512,55 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1785,10 +1785,10 @@
         <v>3.99</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,31 +1809,31 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,10 +2111,10 @@
         <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2135,31 +2135,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>4.44</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>6.6</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2461,31 +2461,31 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
         <v>1.77</v>
@@ -3614,19 +3614,19 @@
         <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -4580,25 +4580,25 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33">
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.14</v>
+        <v>3.55</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U33">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="AA33">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AC33">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG33">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK33">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.9</v>
+        <v>2.28</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>3.07</v>
       </c>
       <c r="Q34">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="AA34">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AC34">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK34">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G35">
@@ -6023,55 +6023,55 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.55</v>
+        <v>1.88</v>
       </c>
       <c r="R35">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>3.15</v>
+        <v>3.84</v>
       </c>
       <c r="AA35">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB35">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AC35">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="U36">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA36">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AC36">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>4.38</v>
       </c>
       <c r="Q37">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="R37">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
+        <v>1.3</v>
+      </c>
+      <c r="Z37">
+        <v>2.99</v>
+      </c>
+      <c r="AA37">
+        <v>1.97</v>
+      </c>
+      <c r="AB37">
+        <v>1.72</v>
+      </c>
+      <c r="AC37">
+        <v>3.38</v>
+      </c>
+      <c r="AD37">
+        <v>1.24</v>
+      </c>
+      <c r="AE37">
+        <v>1.05</v>
+      </c>
+      <c r="AF37">
+        <v>1.87</v>
+      </c>
+      <c r="AG37">
+        <v>1.83</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.29</v>
       </c>
-      <c r="Z37">
-        <v>3.15</v>
-      </c>
-      <c r="AA37">
-        <v>1.92</v>
-      </c>
-      <c r="AB37">
-        <v>1.75</v>
-      </c>
-      <c r="AC37">
-        <v>3.24</v>
-      </c>
-      <c r="AD37">
-        <v>1.26</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
-      <c r="AF37">
-        <v>1.75</v>
-      </c>
-      <c r="AG37">
-        <v>1.97</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.31</v>
-      </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,43 +6503,43 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q38">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AA38">
         <v>1.82</v>
@@ -6554,13 +6554,13 @@
         <v>1.34</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>2.64</v>
       </c>
       <c r="AG38">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>1.93</v>
+        <v>4.24</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q39">
-        <v>1.97</v>
+        <v>4.55</v>
       </c>
       <c r="R39">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U39">
         <v>2.59</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="AA39">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB39">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD39">
         <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AG39">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>2.59</v>
+        <v>1.24</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="O40">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>4.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q40">
-        <v>2.34</v>
+        <v>3.7</v>
       </c>
       <c r="R40">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S40">
+        <v>1.38</v>
+      </c>
+      <c r="T40">
+        <v>2.81</v>
+      </c>
+      <c r="U40">
+        <v>2.75</v>
+      </c>
+      <c r="V40">
+        <v>1.4</v>
+      </c>
+      <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.29</v>
+      </c>
+      <c r="Z40">
+        <v>3.15</v>
+      </c>
+      <c r="AA40">
+        <v>1.92</v>
+      </c>
+      <c r="AB40">
+        <v>1.75</v>
+      </c>
+      <c r="AC40">
+        <v>3.24</v>
+      </c>
+      <c r="AD40">
+        <v>1.26</v>
+      </c>
+      <c r="AE40">
+        <v>1.09</v>
+      </c>
+      <c r="AF40">
+        <v>1.75</v>
+      </c>
+      <c r="AG40">
+        <v>1.97</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.31</v>
+      </c>
+      <c r="AK40">
         <v>1.36</v>
-      </c>
-      <c r="T40">
-        <v>2.88</v>
-      </c>
-      <c r="U40">
-        <v>2.88</v>
-      </c>
-      <c r="V40">
-        <v>1.36</v>
-      </c>
-      <c r="W40">
-        <v>1.06</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.3</v>
-      </c>
-      <c r="Z40">
-        <v>2.99</v>
-      </c>
-      <c r="AA40">
-        <v>1.97</v>
-      </c>
-      <c r="AB40">
-        <v>1.72</v>
-      </c>
-      <c r="AC40">
-        <v>3.38</v>
-      </c>
-      <c r="AD40">
-        <v>1.24</v>
-      </c>
-      <c r="AE40">
-        <v>1.05</v>
-      </c>
-      <c r="AF40">
-        <v>1.87</v>
-      </c>
-      <c r="AG40">
-        <v>1.83</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.29</v>
-      </c>
-      <c r="AK40">
-        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="R41">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7022,50 +7022,50 @@
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
+        <v>1.23</v>
+      </c>
+      <c r="Z41">
+        <v>3.74</v>
+      </c>
+      <c r="AA41">
+        <v>1.81</v>
+      </c>
+      <c r="AB41">
+        <v>2.04</v>
+      </c>
+      <c r="AC41">
+        <v>2.88</v>
+      </c>
+      <c r="AD41">
+        <v>1.33</v>
+      </c>
+      <c r="AE41">
+        <v>1.08</v>
+      </c>
+      <c r="AF41">
+        <v>1.87</v>
+      </c>
+      <c r="AG41">
+        <v>1.83</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.22</v>
       </c>
-      <c r="Z41">
-        <v>3.54</v>
-      </c>
-      <c r="AA41">
-        <v>1.82</v>
-      </c>
-      <c r="AB41">
-        <v>2.03</v>
-      </c>
-      <c r="AC41">
-        <v>2.8</v>
-      </c>
-      <c r="AD41">
-        <v>1.34</v>
-      </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>2.64</v>
-      </c>
-      <c r="AG41">
-        <v>1.42</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.14</v>
-      </c>
       <c r="AK41">
-        <v>4.24</v>
+        <v>2.59</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U42">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="AA42">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB42">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AC42">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q33">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA33">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AC33">
-        <v>3.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK33">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="AA34">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AB34">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q35">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="R35">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.84</v>
+        <v>2.99</v>
       </c>
       <c r="AA35">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AB35">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AC35">
-        <v>2.68</v>
+        <v>3.38</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>2.14</v>
+        <v>4.55</v>
       </c>
       <c r="R36">
         <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="U36">
         <v>2.59</v>
@@ -6204,37 +6204,37 @@
         <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AA36">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB36">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD36">
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG36">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>2.31</v>
+        <v>1.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>2.4</v>
+      </c>
+      <c r="R37">
+        <v>2.3</v>
+      </c>
+      <c r="S37">
+        <v>1.33</v>
+      </c>
+      <c r="T37">
+        <v>3.04</v>
+      </c>
+      <c r="U37">
+        <v>2.56</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.23</v>
+      </c>
+      <c r="Z37">
+        <v>3.6</v>
+      </c>
+      <c r="AA37">
         <v>1.82</v>
       </c>
-      <c r="O37">
-        <v>3.62</v>
-      </c>
-      <c r="P37">
-        <v>4.38</v>
-      </c>
-      <c r="Q37">
-        <v>2.34</v>
-      </c>
-      <c r="R37">
-        <v>2.12</v>
-      </c>
-      <c r="S37">
-        <v>1.36</v>
-      </c>
-      <c r="T37">
-        <v>2.88</v>
-      </c>
-      <c r="U37">
-        <v>2.88</v>
-      </c>
-      <c r="V37">
-        <v>1.36</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.3</v>
-      </c>
-      <c r="Z37">
-        <v>2.99</v>
-      </c>
-      <c r="AA37">
-        <v>1.97</v>
-      </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AC37">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="R39">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U39">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="AA39">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,22 +7164,22 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T42">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U42">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.07</v>
@@ -7191,28 +7191,28 @@
         <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AA42">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB42">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD42">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q34">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="R34">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.84</v>
+        <v>2.99</v>
       </c>
       <c r="AA34">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AB34">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AC34">
-        <v>2.68</v>
+        <v>3.38</v>
       </c>
       <c r="AD34">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.82</v>
+        <v>3.9</v>
       </c>
       <c r="O35">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>4.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q35">
-        <v>2.34</v>
+        <v>4.55</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
       <c r="AA35">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB35">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.55</v>
+        <v>2.4</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U36">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AA36">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AC36">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U37">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="AA37">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB37">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD37">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK37">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="R38">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V38">
         <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AA38">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB38">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
         <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>2.64</v>
+        <v>1.84</v>
       </c>
       <c r="AG38">
-        <v>1.42</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>4.24</v>
+        <v>2.31</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G39">
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.55</v>
+        <v>1.88</v>
       </c>
       <c r="R39">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z39">
-        <v>3.15</v>
+        <v>3.84</v>
       </c>
       <c r="AA39">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AC39">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="AD39">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>1.97</v>
+      </c>
+      <c r="R40">
+        <v>2.32</v>
+      </c>
+      <c r="S40">
+        <v>1.32</v>
+      </c>
+      <c r="T40">
         <v>3.1</v>
       </c>
-      <c r="O40">
-        <v>3.5</v>
-      </c>
-      <c r="P40">
-        <v>2.25</v>
-      </c>
-      <c r="Q40">
-        <v>3.7</v>
-      </c>
-      <c r="R40">
-        <v>2.13</v>
-      </c>
-      <c r="S40">
-        <v>1.38</v>
-      </c>
-      <c r="T40">
-        <v>2.81</v>
-      </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
+        <v>1.06</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.23</v>
+      </c>
+      <c r="Z40">
+        <v>3.74</v>
+      </c>
+      <c r="AA40">
+        <v>1.81</v>
+      </c>
+      <c r="AB40">
+        <v>2.04</v>
+      </c>
+      <c r="AC40">
+        <v>2.88</v>
+      </c>
+      <c r="AD40">
+        <v>1.33</v>
+      </c>
+      <c r="AE40">
         <v>1.08</v>
       </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.29</v>
-      </c>
-      <c r="Z40">
-        <v>3.15</v>
-      </c>
-      <c r="AA40">
-        <v>1.92</v>
-      </c>
-      <c r="AB40">
-        <v>1.75</v>
-      </c>
-      <c r="AC40">
-        <v>3.24</v>
-      </c>
-      <c r="AD40">
-        <v>1.26</v>
-      </c>
-      <c r="AE40">
-        <v>1.09</v>
-      </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG40">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.36</v>
+        <v>2.59</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q41">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="R41">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U41">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7022,34 +7022,34 @@
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="AA41">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB41">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC41">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.87</v>
+        <v>2.64</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>2.59</v>
+        <v>4.24</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.14</v>
+        <v>3.55</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S42">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U42">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="AA42">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AC42">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG42">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK42">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -644,22 +644,22 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
         <v>1.99</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
         <v>2.9</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
         <v>1.04</v>
@@ -674,7 +674,7 @@
         <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="P5">
-        <v>10.9</v>
+        <v>7.25</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="S5">
         <v>1.18</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="U5">
         <v>2.03</v>
@@ -1163,7 +1163,7 @@
         <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
         <v>2.66</v>
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="AD5">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AE5">
         <v>1.24</v>
@@ -1181,7 +1181,7 @@
         <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK5">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -1468,37 +1468,37 @@
         <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z7">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1507,7 +1507,7 @@
         <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
         <v>2.08</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="O14">
         <v>3.11</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="R14">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U14">
         <v>3.35</v>
@@ -2630,16 +2630,16 @@
         <v>2.49</v>
       </c>
       <c r="AA14">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AB14">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
         <v>4.3</v>
       </c>
       <c r="AD14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE14">
         <v>1.01</v>
@@ -2648,7 +2648,7 @@
         <v>2.01</v>
       </c>
       <c r="AG14">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AK14">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
         <v>2.29</v>
@@ -2944,37 +2944,37 @@
         <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.75</v>
+        <v>4.91</v>
       </c>
       <c r="AA16">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AC16">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AD16">
         <v>1.56</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,46 +3080,46 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>3.2</v>
       </c>
       <c r="P17">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
         <v>2.62</v>
       </c>
       <c r="U17">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="V17">
         <v>1.31</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
         <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB17">
         <v>1.66</v>
@@ -3128,16 +3128,16 @@
         <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="R18">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="S18">
         <v>1.14</v>
       </c>
       <c r="T18">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="U18">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="W18">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="AA18">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AB18">
-        <v>5.6</v>
+        <v>3.58</v>
       </c>
       <c r="AC18">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="AD18">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AE18">
-        <v>2.11</v>
+        <v>1.51</v>
       </c>
       <c r="AF18">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="AG18">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK18">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,28 +3409,28 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R19">
         <v>1.82</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="V19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,22 +3439,22 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AA19">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AB19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3463,7 +3463,7 @@
         <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4058,55 +4058,55 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
         <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA23">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AC23">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
         <v>1.15</v>
@@ -4115,7 +4115,7 @@
         <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="O24">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q24">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V24">
         <v>1.9</v>
       </c>
       <c r="W24">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,28 +4257,28 @@
         <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB24">
-        <v>3.41</v>
+        <v>3.57</v>
       </c>
       <c r="AC24">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD24">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AE24">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF24">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AG24">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4722,52 +4722,52 @@
         <v>3.6</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB27">
         <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AG27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="O28">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>1.53</v>
@@ -4888,16 +4888,16 @@
         <v>2.88</v>
       </c>
       <c r="S28">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V28">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W28">
         <v>1.2</v>
@@ -4909,19 +4909,19 @@
         <v>1.06</v>
       </c>
       <c r="Z28">
-        <v>6.5</v>
+        <v>6.82</v>
       </c>
       <c r="AA28">
         <v>1.36</v>
       </c>
       <c r="AB28">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AC28">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD28">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AE28">
         <v>1.33</v>
@@ -4930,7 +4930,7 @@
         <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK28">
         <v>4.2</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
         <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U29">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="V29">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z29">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB29">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AC29">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
         <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,16 +5202,16 @@
         <v>1.59</v>
       </c>
       <c r="O30">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>5.17</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
         <v>1.39</v>
@@ -5232,31 +5232,31 @@
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
         <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC30">
         <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="O33">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U33">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.13</v>
@@ -5730,13 +5730,13 @@
         <v>1.58</v>
       </c>
       <c r="AB33">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC33">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
         <v>1.17</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O34">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="P34">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="R34">
         <v>2.12</v>
@@ -5890,10 +5890,10 @@
         <v>2.99</v>
       </c>
       <c r="AA34">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB34">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC34">
         <v>3.38</v>
@@ -5902,13 +5902,13 @@
         <v>1.24</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.35</v>
@@ -6035,13 +6035,13 @@
         <v>2.94</v>
       </c>
       <c r="U35">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V35">
         <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6053,25 +6053,25 @@
         <v>3.54</v>
       </c>
       <c r="AA35">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB35">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC35">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD35">
         <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>2.4</v>
+        <v>3.74</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U36">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="AA36">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB36">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD36">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG36">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>4.38</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>6.35</v>
       </c>
       <c r="Q37">
-        <v>3.7</v>
+        <v>1.97</v>
       </c>
       <c r="R37">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
+        <v>1.1</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>3.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.81</v>
+      </c>
+      <c r="AB37">
+        <v>2.04</v>
+      </c>
+      <c r="AC37">
+        <v>2.85</v>
+      </c>
+      <c r="AD37">
+        <v>1.33</v>
+      </c>
+      <c r="AE37">
         <v>1.08</v>
       </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.29</v>
-      </c>
-      <c r="Z37">
-        <v>3.15</v>
-      </c>
-      <c r="AA37">
-        <v>1.92</v>
-      </c>
-      <c r="AB37">
-        <v>1.75</v>
-      </c>
-      <c r="AC37">
-        <v>3.24</v>
-      </c>
-      <c r="AD37">
-        <v>1.26</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG37">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q38">
-        <v>2.14</v>
+        <v>3.54</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U38">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
+        <v>1.3</v>
+      </c>
+      <c r="Z38">
+        <v>3.15</v>
+      </c>
+      <c r="AA38">
+        <v>1.96</v>
+      </c>
+      <c r="AB38">
+        <v>1.79</v>
+      </c>
+      <c r="AC38">
+        <v>3.44</v>
+      </c>
+      <c r="AD38">
         <v>1.23</v>
       </c>
-      <c r="Z38">
-        <v>3.44</v>
-      </c>
-      <c r="AA38">
-        <v>1.86</v>
-      </c>
-      <c r="AB38">
-        <v>1.98</v>
-      </c>
-      <c r="AC38">
-        <v>2.83</v>
-      </c>
-      <c r="AD38">
-        <v>1.33</v>
-      </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G39">
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U39">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AA39">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB39">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC39">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="AD39">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q40">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S40">
         <v>1.32</v>
@@ -6850,43 +6850,43 @@
         <v>3.1</v>
       </c>
       <c r="U40">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AA40">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD40">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG40">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="O41">
-        <v>5.85</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
-        <v>15</v>
+        <v>3.8</v>
       </c>
       <c r="Q41">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="R41">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V41">
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AA41">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB41">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC41">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
         <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>2.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG41">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q42">
-        <v>3.55</v>
+        <v>1.65</v>
       </c>
       <c r="R42">
-        <v>2.03</v>
+        <v>2.63</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U42">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="AA42">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB42">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD42">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="AG42">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,19 +7321,19 @@
         <v>1.31</v>
       </c>
       <c r="O43">
-        <v>4.92</v>
+        <v>4.55</v>
       </c>
       <c r="P43">
-        <v>9.800000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="Q43">
         <v>1.8</v>
       </c>
       <c r="R43">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
         <v>2.7</v>
@@ -7342,40 +7342,40 @@
         <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
         <v>2.17</v>
       </c>
       <c r="AG43">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU43"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3578,55 +3578,55 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="R20">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U20">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
+        <v>1.5</v>
+      </c>
+      <c r="W20">
+        <v>1.12</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.16</v>
+      </c>
+      <c r="Z20">
+        <v>4.15</v>
+      </c>
+      <c r="AA20">
+        <v>1.61</v>
+      </c>
+      <c r="AB20">
+        <v>2.15</v>
+      </c>
+      <c r="AC20">
+        <v>2.55</v>
+      </c>
+      <c r="AD20">
+        <v>1.47</v>
+      </c>
+      <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
         <v>1.44</v>
       </c>
-      <c r="W20">
-        <v>1.08</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.22</v>
-      </c>
-      <c r="Z20">
-        <v>3.5</v>
-      </c>
-      <c r="AA20">
-        <v>1.77</v>
-      </c>
-      <c r="AB20">
-        <v>1.94</v>
-      </c>
-      <c r="AC20">
-        <v>2.95</v>
-      </c>
-      <c r="AD20">
-        <v>1.3</v>
-      </c>
-      <c r="AE20">
-        <v>1.1</v>
-      </c>
-      <c r="AF20">
-        <v>1.62</v>
-      </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="O21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Q21">
-        <v>6.36</v>
+        <v>5.25</v>
       </c>
       <c r="R21">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S21">
         <v>1.23</v>
@@ -3753,10 +3753,10 @@
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3765,31 +3765,31 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>2.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
         <v>1.07</v>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="O22">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="P22">
-        <v>7.47</v>
+        <v>5.55</v>
       </c>
       <c r="Q22">
         <v>1.83</v>
       </c>
       <c r="R22">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T22">
         <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="V22">
         <v>1.63</v>
@@ -3928,7 +3928,7 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
         <v>5.75</v>
@@ -3952,7 +3952,7 @@
         <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.54</v>
+        <v>2.98</v>
       </c>
       <c r="P25">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="Q25">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="R25">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V25">
         <v>1.44</v>
@@ -4414,7 +4414,7 @@
         <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.23</v>
@@ -4423,25 +4423,25 @@
         <v>3.96</v>
       </c>
       <c r="AA25">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB25">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG25">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.81</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-03 15:15:00</t>
+          <t>2026-08-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,81 +4873,81 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>10</v>
+        <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
+        <v>2.1</v>
+      </c>
+      <c r="S28">
+        <v>1.39</v>
+      </c>
+      <c r="T28">
         <v>2.88</v>
       </c>
-      <c r="S28">
-        <v>1.18</v>
-      </c>
-      <c r="T28">
-        <v>4.8</v>
-      </c>
       <c r="U28">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
+        <v>1.28</v>
+      </c>
+      <c r="Z28">
+        <v>3.5</v>
+      </c>
+      <c r="AA28">
+        <v>1.92</v>
+      </c>
+      <c r="AB28">
+        <v>1.79</v>
+      </c>
+      <c r="AC28">
+        <v>3.4</v>
+      </c>
+      <c r="AD28">
+        <v>1.29</v>
+      </c>
+      <c r="AE28">
         <v>1.06</v>
       </c>
-      <c r="Z28">
-        <v>6.82</v>
-      </c>
-      <c r="AA28">
+      <c r="AF28">
+        <v>1.69</v>
+      </c>
+      <c r="AG28">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.31</v>
+      </c>
+      <c r="AK28">
         <v>1.36</v>
       </c>
-      <c r="AB28">
-        <v>3</v>
-      </c>
-      <c r="AC28">
-        <v>1.87</v>
-      </c>
-      <c r="AD28">
-        <v>1.93</v>
-      </c>
-      <c r="AE28">
-        <v>1.33</v>
-      </c>
-      <c r="AF28">
-        <v>1.8</v>
-      </c>
-      <c r="AG28">
-        <v>1.93</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.08</v>
-      </c>
-      <c r="AK28">
-        <v>4.2</v>
-      </c>
       <c r="AL28">
         <v>0</v>
       </c>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-03 15:30:00</t>
+          <t>2026-08-03 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="P29">
+        <v>10</v>
+      </c>
+      <c r="Q29">
+        <v>1.53</v>
+      </c>
+      <c r="R29">
+        <v>2.88</v>
+      </c>
+      <c r="S29">
+        <v>1.18</v>
+      </c>
+      <c r="T29">
+        <v>4.8</v>
+      </c>
+      <c r="U29">
+        <v>1.9</v>
+      </c>
+      <c r="V29">
+        <v>1.75</v>
+      </c>
+      <c r="W29">
+        <v>1.2</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.06</v>
+      </c>
+      <c r="Z29">
+        <v>6.82</v>
+      </c>
+      <c r="AA29">
+        <v>1.36</v>
+      </c>
+      <c r="AB29">
+        <v>3</v>
+      </c>
+      <c r="AC29">
+        <v>1.87</v>
+      </c>
+      <c r="AD29">
+        <v>1.93</v>
+      </c>
+      <c r="AE29">
+        <v>1.33</v>
+      </c>
+      <c r="AF29">
+        <v>1.8</v>
+      </c>
+      <c r="AG29">
+        <v>1.93</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.08</v>
+      </c>
+      <c r="AK29">
         <v>4.2</v>
-      </c>
-      <c r="Q29">
-        <v>2.1</v>
-      </c>
-      <c r="R29">
-        <v>2.33</v>
-      </c>
-      <c r="S29">
-        <v>1.35</v>
-      </c>
-      <c r="T29">
-        <v>3.18</v>
-      </c>
-      <c r="U29">
-        <v>2.6</v>
-      </c>
-      <c r="V29">
-        <v>1.44</v>
-      </c>
-      <c r="W29">
-        <v>1.06</v>
-      </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.21</v>
-      </c>
-      <c r="Z29">
-        <v>3.7</v>
-      </c>
-      <c r="AA29">
-        <v>1.77</v>
-      </c>
-      <c r="AB29">
-        <v>1.97</v>
-      </c>
-      <c r="AC29">
-        <v>2.83</v>
-      </c>
-      <c r="AD29">
-        <v>1.38</v>
-      </c>
-      <c r="AE29">
-        <v>1.09</v>
-      </c>
-      <c r="AF29">
-        <v>1.7</v>
-      </c>
-      <c r="AG29">
-        <v>2.04</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.24</v>
-      </c>
-      <c r="AK29">
-        <v>1.98</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
         <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="U30">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AC30">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-03 16:00:00</t>
+          <t>2026-08-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>4.15</v>
+        <v>2.25</v>
       </c>
       <c r="R31">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="U31">
-        <v>4.33</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
         <v>1.02</v>
       </c>
-      <c r="X31">
-        <v>1.18</v>
-      </c>
       <c r="Y31">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="Z31">
-        <v>2.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA31">
+        <v>2</v>
+      </c>
+      <c r="AB31">
+        <v>1.77</v>
+      </c>
+      <c r="AC31">
         <v>3.14</v>
       </c>
-      <c r="AB31">
+      <c r="AD31">
         <v>1.28</v>
       </c>
-      <c r="AC31">
-        <v>6.4</v>
-      </c>
-      <c r="AD31">
-        <v>1.05</v>
-      </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AG31">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="P32">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="Q32">
-        <v>2.36</v>
+        <v>3.64</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="T32">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="U32">
-        <v>2.91</v>
+        <v>4.33</v>
       </c>
       <c r="V32">
+        <v>1.17</v>
+      </c>
+      <c r="W32">
+        <v>1.02</v>
+      </c>
+      <c r="X32">
+        <v>1.14</v>
+      </c>
+      <c r="Y32">
+        <v>1.71</v>
+      </c>
+      <c r="Z32">
+        <v>2.06</v>
+      </c>
+      <c r="AA32">
+        <v>3.08</v>
+      </c>
+      <c r="AB32">
+        <v>1.28</v>
+      </c>
+      <c r="AC32">
+        <v>6.4</v>
+      </c>
+      <c r="AD32">
+        <v>1.11</v>
+      </c>
+      <c r="AE32">
+        <v>1.02</v>
+      </c>
+      <c r="AF32">
+        <v>2.2</v>
+      </c>
+      <c r="AG32">
+        <v>1.44</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.33</v>
       </c>
-      <c r="W32">
-        <v>1.05</v>
-      </c>
-      <c r="X32">
-        <v>1.01</v>
-      </c>
-      <c r="Y32">
-        <v>1.3</v>
-      </c>
-      <c r="Z32">
-        <v>2.97</v>
-      </c>
-      <c r="AA32">
-        <v>2.02</v>
-      </c>
-      <c r="AB32">
-        <v>1.71</v>
-      </c>
-      <c r="AC32">
-        <v>3.5</v>
-      </c>
-      <c r="AD32">
-        <v>1.22</v>
-      </c>
-      <c r="AE32">
-        <v>1.04</v>
-      </c>
-      <c r="AF32">
-        <v>1.88</v>
-      </c>
-      <c r="AG32">
-        <v>1.81</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.23</v>
-      </c>
       <c r="AK32">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-03 21:00:00</t>
+          <t>2026-08-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="O33">
+        <v>3.35</v>
+      </c>
+      <c r="P33">
+        <v>4.15</v>
+      </c>
+      <c r="Q33">
+        <v>2.36</v>
+      </c>
+      <c r="R33">
+        <v>2.05</v>
+      </c>
+      <c r="S33">
+        <v>1.4</v>
+      </c>
+      <c r="T33">
+        <v>2.62</v>
+      </c>
+      <c r="U33">
+        <v>2.91</v>
+      </c>
+      <c r="V33">
+        <v>1.33</v>
+      </c>
+      <c r="W33">
+        <v>1.05</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.3</v>
+      </c>
+      <c r="Z33">
+        <v>2.97</v>
+      </c>
+      <c r="AA33">
+        <v>2.02</v>
+      </c>
+      <c r="AB33">
+        <v>1.71</v>
+      </c>
+      <c r="AC33">
         <v>3.5</v>
       </c>
-      <c r="P33">
-        <v>3.1</v>
-      </c>
-      <c r="Q33">
-        <v>2.65</v>
-      </c>
-      <c r="R33">
-        <v>2.35</v>
-      </c>
-      <c r="S33">
-        <v>1.31</v>
-      </c>
-      <c r="T33">
-        <v>3.15</v>
-      </c>
-      <c r="U33">
-        <v>2.5</v>
-      </c>
-      <c r="V33">
-        <v>1.5</v>
-      </c>
-      <c r="W33">
-        <v>1.13</v>
-      </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.15</v>
-      </c>
-      <c r="Z33">
-        <v>4.3</v>
-      </c>
-      <c r="AA33">
-        <v>1.58</v>
-      </c>
-      <c r="AB33">
-        <v>2.16</v>
-      </c>
-      <c r="AC33">
-        <v>2.45</v>
-      </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="O34">
-        <v>3.64</v>
+        <v>5.35</v>
       </c>
       <c r="P34">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="Q34">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AA34">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="AG34">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AK34">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5954,1473 +5954,6 @@
         <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Sparta Praha</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Olympique Lyonnais</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N35">
-        <v>4</v>
-      </c>
-      <c r="O35">
-        <v>3.6</v>
-      </c>
-      <c r="P35">
-        <v>1.87</v>
-      </c>
-      <c r="Q35">
-        <v>4</v>
-      </c>
-      <c r="R35">
-        <v>2.3</v>
-      </c>
-      <c r="S35">
-        <v>1.35</v>
-      </c>
-      <c r="T35">
-        <v>2.94</v>
-      </c>
-      <c r="U35">
-        <v>2.63</v>
-      </c>
-      <c r="V35">
-        <v>1.44</v>
-      </c>
-      <c r="W35">
-        <v>1.1</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.22</v>
-      </c>
-      <c r="Z35">
-        <v>3.54</v>
-      </c>
-      <c r="AA35">
-        <v>1.86</v>
-      </c>
-      <c r="AB35">
-        <v>1.99</v>
-      </c>
-      <c r="AC35">
-        <v>2.85</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.11</v>
-      </c>
-      <c r="AF35">
-        <v>1.7</v>
-      </c>
-      <c r="AG35">
-        <v>2.04</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
-      <c r="AK35">
-        <v>1.2</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Hapoel Be'er Sheva</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36">
-        <v>3.5</v>
-      </c>
-      <c r="P36">
-        <v>2.25</v>
-      </c>
-      <c r="Q36">
-        <v>3.74</v>
-      </c>
-      <c r="R36">
-        <v>2.17</v>
-      </c>
-      <c r="S36">
-        <v>1.38</v>
-      </c>
-      <c r="T36">
-        <v>2.81</v>
-      </c>
-      <c r="U36">
-        <v>2.81</v>
-      </c>
-      <c r="V36">
-        <v>1.38</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.28</v>
-      </c>
-      <c r="Z36">
-        <v>3.15</v>
-      </c>
-      <c r="AA36">
-        <v>2.02</v>
-      </c>
-      <c r="AB36">
-        <v>1.83</v>
-      </c>
-      <c r="AC36">
-        <v>3.3</v>
-      </c>
-      <c r="AD36">
-        <v>1.25</v>
-      </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
-      <c r="AF36">
-        <v>1.72</v>
-      </c>
-      <c r="AG36">
-        <v>1.96</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.67</v>
-      </c>
-      <c r="AK36">
-        <v>1.3</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Fenerbahçe</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Sturm Graz</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N37">
-        <v>1.5</v>
-      </c>
-      <c r="O37">
-        <v>4.38</v>
-      </c>
-      <c r="P37">
-        <v>6.35</v>
-      </c>
-      <c r="Q37">
-        <v>1.97</v>
-      </c>
-      <c r="R37">
-        <v>2.32</v>
-      </c>
-      <c r="S37">
-        <v>1.3</v>
-      </c>
-      <c r="T37">
-        <v>3.15</v>
-      </c>
-      <c r="U37">
-        <v>2.59</v>
-      </c>
-      <c r="V37">
-        <v>1.44</v>
-      </c>
-      <c r="W37">
-        <v>1.1</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.2</v>
-      </c>
-      <c r="Z37">
-        <v>3.74</v>
-      </c>
-      <c r="AA37">
-        <v>1.81</v>
-      </c>
-      <c r="AB37">
-        <v>2.04</v>
-      </c>
-      <c r="AC37">
-        <v>2.85</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.08</v>
-      </c>
-      <c r="AF37">
-        <v>1.87</v>
-      </c>
-      <c r="AG37">
-        <v>1.83</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.22</v>
-      </c>
-      <c r="AK37">
-        <v>2.63</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>-1</v>
-      </c>
-      <c r="AN37">
-        <v>-1</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>-1</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>FC Avan Academy</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Celje</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N38">
-        <v>2.92</v>
-      </c>
-      <c r="O38">
-        <v>3.28</v>
-      </c>
-      <c r="P38">
-        <v>2.45</v>
-      </c>
-      <c r="Q38">
-        <v>3.54</v>
-      </c>
-      <c r="R38">
-        <v>2.03</v>
-      </c>
-      <c r="S38">
-        <v>1.36</v>
-      </c>
-      <c r="T38">
-        <v>2.88</v>
-      </c>
-      <c r="U38">
-        <v>2.89</v>
-      </c>
-      <c r="V38">
-        <v>1.36</v>
-      </c>
-      <c r="W38">
-        <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1.3</v>
-      </c>
-      <c r="Z38">
-        <v>3.15</v>
-      </c>
-      <c r="AA38">
-        <v>1.96</v>
-      </c>
-      <c r="AB38">
-        <v>1.79</v>
-      </c>
-      <c r="AC38">
-        <v>3.44</v>
-      </c>
-      <c r="AD38">
-        <v>1.23</v>
-      </c>
-      <c r="AE38">
-        <v>1.04</v>
-      </c>
-      <c r="AF38">
-        <v>1.76</v>
-      </c>
-      <c r="AG38">
-        <v>1.96</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.25</v>
-      </c>
-      <c r="AK38">
-        <v>1.36</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
-        <v>-1</v>
-      </c>
-      <c r="AN38">
-        <v>-1</v>
-      </c>
-      <c r="AO38">
-        <v>-1</v>
-      </c>
-      <c r="AP38">
-        <v>-1</v>
-      </c>
-      <c r="AQ38">
-        <v>0</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>0</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NEC</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>2.14</v>
-      </c>
-      <c r="R39">
-        <v>2.15</v>
-      </c>
-      <c r="S39">
-        <v>1.38</v>
-      </c>
-      <c r="T39">
-        <v>2.81</v>
-      </c>
-      <c r="U39">
-        <v>2.63</v>
-      </c>
-      <c r="V39">
-        <v>1.44</v>
-      </c>
-      <c r="W39">
-        <v>1.07</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.23</v>
-      </c>
-      <c r="Z39">
-        <v>3.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.86</v>
-      </c>
-      <c r="AB39">
-        <v>1.98</v>
-      </c>
-      <c r="AC39">
-        <v>2.83</v>
-      </c>
-      <c r="AD39">
-        <v>1.33</v>
-      </c>
-      <c r="AE39">
-        <v>1.1</v>
-      </c>
-      <c r="AF39">
-        <v>1.84</v>
-      </c>
-      <c r="AG39">
-        <v>1.86</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.27</v>
-      </c>
-      <c r="AK39">
-        <v>2.31</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>-1</v>
-      </c>
-      <c r="AN39">
-        <v>-1</v>
-      </c>
-      <c r="AO39">
-        <v>-1</v>
-      </c>
-      <c r="AP39">
-        <v>-1</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AGF</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sabah</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N40">
-        <v>1.42</v>
-      </c>
-      <c r="O40">
-        <v>4.58</v>
-      </c>
-      <c r="P40">
-        <v>7.5</v>
-      </c>
-      <c r="Q40">
-        <v>1.83</v>
-      </c>
-      <c r="R40">
-        <v>2.36</v>
-      </c>
-      <c r="S40">
-        <v>1.32</v>
-      </c>
-      <c r="T40">
-        <v>3.1</v>
-      </c>
-      <c r="U40">
-        <v>2.4</v>
-      </c>
-      <c r="V40">
-        <v>1.47</v>
-      </c>
-      <c r="W40">
-        <v>1.1</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.19</v>
-      </c>
-      <c r="Z40">
-        <v>3.84</v>
-      </c>
-      <c r="AA40">
-        <v>1.73</v>
-      </c>
-      <c r="AB40">
-        <v>2.07</v>
-      </c>
-      <c r="AC40">
-        <v>2.68</v>
-      </c>
-      <c r="AD40">
-        <v>1.37</v>
-      </c>
-      <c r="AE40">
-        <v>1.11</v>
-      </c>
-      <c r="AF40">
-        <v>1.9</v>
-      </c>
-      <c r="AG40">
-        <v>1.78</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.2</v>
-      </c>
-      <c r="AK40">
-        <v>2.84</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mjällby</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Slovan Bratislava</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N41">
-        <v>1.9</v>
-      </c>
-      <c r="O41">
-        <v>3.7</v>
-      </c>
-      <c r="P41">
-        <v>3.8</v>
-      </c>
-      <c r="Q41">
-        <v>2.35</v>
-      </c>
-      <c r="R41">
-        <v>2.23</v>
-      </c>
-      <c r="S41">
-        <v>1.33</v>
-      </c>
-      <c r="T41">
-        <v>3.04</v>
-      </c>
-      <c r="U41">
-        <v>2.56</v>
-      </c>
-      <c r="V41">
-        <v>1.44</v>
-      </c>
-      <c r="W41">
-        <v>1.07</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.23</v>
-      </c>
-      <c r="Z41">
-        <v>3.6</v>
-      </c>
-      <c r="AA41">
-        <v>1.79</v>
-      </c>
-      <c r="AB41">
-        <v>1.99</v>
-      </c>
-      <c r="AC41">
-        <v>2.88</v>
-      </c>
-      <c r="AD41">
-        <v>1.34</v>
-      </c>
-      <c r="AE41">
-        <v>1.12</v>
-      </c>
-      <c r="AF41">
-        <v>1.68</v>
-      </c>
-      <c r="AG41">
-        <v>2.04</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.22</v>
-      </c>
-      <c r="AK41">
-        <v>1.83</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Kauno Žalgiris</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N42">
-        <v>1.2</v>
-      </c>
-      <c r="O42">
-        <v>6</v>
-      </c>
-      <c r="P42">
-        <v>19</v>
-      </c>
-      <c r="Q42">
-        <v>1.65</v>
-      </c>
-      <c r="R42">
-        <v>2.63</v>
-      </c>
-      <c r="S42">
-        <v>1.36</v>
-      </c>
-      <c r="T42">
-        <v>2.89</v>
-      </c>
-      <c r="U42">
-        <v>2.59</v>
-      </c>
-      <c r="V42">
-        <v>1.44</v>
-      </c>
-      <c r="W42">
-        <v>1.06</v>
-      </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>1.22</v>
-      </c>
-      <c r="Z42">
-        <v>3.54</v>
-      </c>
-      <c r="AA42">
-        <v>1.82</v>
-      </c>
-      <c r="AB42">
-        <v>1.99</v>
-      </c>
-      <c r="AC42">
-        <v>2.88</v>
-      </c>
-      <c r="AD42">
-        <v>1.34</v>
-      </c>
-      <c r="AE42">
-        <v>1.12</v>
-      </c>
-      <c r="AF42">
-        <v>2.5</v>
-      </c>
-      <c r="AG42">
-        <v>1.44</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.1</v>
-      </c>
-      <c r="AK42">
-        <v>4.1</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>2026-08-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Delfin SC</t>
-        </is>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N43">
-        <v>1.31</v>
-      </c>
-      <c r="O43">
-        <v>4.55</v>
-      </c>
-      <c r="P43">
-        <v>8.65</v>
-      </c>
-      <c r="Q43">
-        <v>1.8</v>
-      </c>
-      <c r="R43">
-        <v>2.2</v>
-      </c>
-      <c r="S43">
-        <v>1.38</v>
-      </c>
-      <c r="T43">
-        <v>2.7</v>
-      </c>
-      <c r="U43">
-        <v>2.62</v>
-      </c>
-      <c r="V43">
-        <v>1.4</v>
-      </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.29</v>
-      </c>
-      <c r="Z43">
-        <v>3.5</v>
-      </c>
-      <c r="AA43">
-        <v>1.88</v>
-      </c>
-      <c r="AB43">
-        <v>1.83</v>
-      </c>
-      <c r="AC43">
-        <v>3.14</v>
-      </c>
-      <c r="AD43">
-        <v>1.27</v>
-      </c>
-      <c r="AE43">
-        <v>1.06</v>
-      </c>
-      <c r="AF43">
-        <v>2.17</v>
-      </c>
-      <c r="AG43">
-        <v>1.58</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.18</v>
-      </c>
-      <c r="AK43">
-        <v>3.09</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>-1</v>
-      </c>
-      <c r="AN43">
-        <v>-1</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>-1</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
         <is>
           <t>2026-08-03 21:00:00</t>
         </is>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R2">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA2">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK2">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>5.75</v>
       </c>
       <c r="P5">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
         <v>2.88</v>
@@ -1142,7 +1142,7 @@
         <v>1.18</v>
       </c>
       <c r="T5">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="U5">
         <v>2.03</v>
@@ -1157,31 +1157,31 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
         <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AC5">
         <v>2</v>
       </c>
       <c r="AD5">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AE5">
         <v>1.24</v>
       </c>
       <c r="AF5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK5">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1453,28 +1453,28 @@
         <v>1.8</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q7">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T7">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.04</v>
@@ -1483,13 +1483,13 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
@@ -1498,16 +1498,16 @@
         <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
         <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="AK14">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,13 +2760,13 @@
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
         <v>1.41</v>
@@ -2793,13 +2793,13 @@
         <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB15">
         <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
         <v>1.24</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2932,25 +2932,25 @@
         <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U16">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
         <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
         <v>4.91</v>
@@ -2962,7 +2962,7 @@
         <v>2.39</v>
       </c>
       <c r="AC16">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AD16">
         <v>1.56</v>
@@ -2971,10 +2971,10 @@
         <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3098,13 +3098,13 @@
         <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3252,22 +3252,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="S18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T18">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W18">
         <v>1.25</v>
@@ -3276,31 +3276,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AA18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AB18">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AC18">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AD18">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="AE18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF18">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK18">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P19">
         <v>2.85</v>
@@ -3418,52 +3418,52 @@
         <v>2.56</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="T19">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
+        <v>2.85</v>
+      </c>
+      <c r="V19">
+        <v>1.29</v>
+      </c>
+      <c r="W19">
+        <v>1.01</v>
+      </c>
+      <c r="X19">
+        <v>1.09</v>
+      </c>
+      <c r="Y19">
+        <v>1.3</v>
+      </c>
+      <c r="Z19">
         <v>3.05</v>
       </c>
-      <c r="V19">
-        <v>1.3</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>1.34</v>
-      </c>
-      <c r="Z19">
-        <v>3</v>
-      </c>
       <c r="AA19">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD19">
         <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
         <v>3.6</v>
@@ -4082,13 +4082,13 @@
         <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.18</v>
@@ -4097,19 +4097,19 @@
         <v>4.6</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
         <v>1.5</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P24">
         <v>1.97</v>
       </c>
       <c r="Q24">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S24">
         <v>1.14</v>
@@ -4242,10 +4242,10 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="W24">
         <v>1.25</v>
@@ -4257,19 +4257,19 @@
         <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA24">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AB24">
-        <v>3.57</v>
+        <v>3.7</v>
       </c>
       <c r="AC24">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AD24">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AE24">
         <v>1.52</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R28">
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD28">
         <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,25 +5042,25 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R29">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U29">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V29">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W29">
         <v>1.2</v>
@@ -5072,7 +5072,7 @@
         <v>1.06</v>
       </c>
       <c r="Z29">
-        <v>6.82</v>
+        <v>6.5</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5084,7 +5084,7 @@
         <v>1.87</v>
       </c>
       <c r="AD29">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE29">
         <v>1.33</v>
@@ -5093,7 +5093,7 @@
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,37 +5199,37 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U30">
         <v>2.6</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
         <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.21</v>
@@ -5241,10 +5241,10 @@
         <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD30">
         <v>1.38</v>
@@ -5253,10 +5253,10 @@
         <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG30">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5365,16 +5365,16 @@
         <v>1.59</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>5.17</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.39</v>
@@ -5383,7 +5383,7 @@
         <v>2.66</v>
       </c>
       <c r="U31">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V31">
         <v>1.36</v>
@@ -5395,16 +5395,16 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA31">
         <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC31">
         <v>3.14</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK31">
         <v>2</v>
@@ -5703,19 +5703,19 @@
         <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U33">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5724,16 +5724,16 @@
         <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AA33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD33">
         <v>1.22</v>
@@ -5742,7 +5742,7 @@
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
         <v>1.81</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O34">
-        <v>5.35</v>
+        <v>4.79</v>
       </c>
       <c r="P34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>1.67</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="U34">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5884,28 +5884,28 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA34">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
         <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG34">
         <v>1.58</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AK34">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1465,13 +1465,13 @@
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
         <v>1.4</v>
@@ -1480,34 +1480,34 @@
         <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB7">
+        <v>1.75</v>
+      </c>
+      <c r="AC7">
+        <v>3.5</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.06</v>
+      </c>
+      <c r="AF7">
         <v>1.8</v>
       </c>
-      <c r="AC7">
-        <v>3.34</v>
-      </c>
-      <c r="AD7">
-        <v>1.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.05</v>
-      </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>1.84</v>
-      </c>
-      <c r="AG7">
-        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.99</v>
+        <v>4.7</v>
       </c>
       <c r="Q9">
         <v>2.23</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
         <v>1.85</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q11">
         <v>3.25</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="Q12">
         <v>2.02</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
         <v>2.08</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="O13">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="Q13">
         <v>1.92</v>
@@ -2941,7 +2941,7 @@
         <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
         <v>1.1</v>
@@ -2953,22 +2953,22 @@
         <v>1.12</v>
       </c>
       <c r="Z16">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
         <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AC16">
         <v>2.45</v>
       </c>
       <c r="AD16">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
@@ -3089,25 +3089,25 @@
         <v>3.05</v>
       </c>
       <c r="Q17">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="V17">
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3578,55 +3578,55 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T20">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="AA20">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB20">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AD20">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AK20">
         <v>1.4</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="O21">
         <v>4.6</v>
       </c>
       <c r="P21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q21">
-        <v>5.25</v>
+        <v>6.46</v>
       </c>
       <c r="R21">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.23</v>
@@ -3753,10 +3753,10 @@
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3765,31 +3765,31 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG21">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
         <v>1.07</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O22">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="P22">
-        <v>5.55</v>
+        <v>6.05</v>
       </c>
       <c r="Q22">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R22">
         <v>2.45</v>
@@ -3916,7 +3916,7 @@
         <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
         <v>1.63</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
         <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC22">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AD22">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF22">
         <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O25">
         <v>2.98</v>
       </c>
       <c r="P25">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U25">
         <v>2.56</v>
@@ -4414,7 +4414,7 @@
         <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y25">
         <v>1.23</v>
@@ -4426,7 +4426,7 @@
         <v>1.63</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
         <v>2.55</v>
@@ -4435,7 +4435,7 @@
         <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
         <v>1.5</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4888,46 +4888,46 @@
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
         <v>2.69</v>
       </c>
       <c r="U28">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
         <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG28">
         <v>2.01</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,31 +5045,31 @@
         <v>11</v>
       </c>
       <c r="Q29">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="S29">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
         <v>4.33</v>
       </c>
       <c r="U29">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V29">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
         <v>6.5</v>
@@ -5078,13 +5078,13 @@
         <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AC29">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD29">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE29">
         <v>1.33</v>
@@ -5093,7 +5093,7 @@
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
         <v>2.17</v>
@@ -5220,10 +5220,10 @@
         <v>2.95</v>
       </c>
       <c r="U30">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
         <v>1.06</v>
@@ -5235,28 +5235,28 @@
         <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC30">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
         <v>1.98</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P32">
         <v>2.95</v>
@@ -5555,10 +5555,10 @@
         <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Y32">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Z32">
         <v>2.06</v>
@@ -5567,10 +5567,10 @@
         <v>3.08</v>
       </c>
       <c r="AB32">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC32">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AD32">
         <v>1.11</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK32">
         <v>1.42</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3098,13 +3098,13 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3119,7 +3119,7 @@
         <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AB17">
         <v>1.66</v>
@@ -3424,28 +3424,28 @@
         <v>1.53</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="U19">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="V19">
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
@@ -3454,16 +3454,16 @@
         <v>3.58</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3427,25 +3427,25 @@
         <v>2.32</v>
       </c>
       <c r="U19">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
         <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
@@ -3454,10 +3454,10 @@
         <v>3.58</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5039,31 +5039,31 @@
         <v>1.16</v>
       </c>
       <c r="O29">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="P29">
         <v>11</v>
       </c>
       <c r="Q29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R29">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V29">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,28 +5072,28 @@
         <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>6.5</v>
+        <v>6.82</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AC29">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD29">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5700,19 +5700,19 @@
         <v>2.36</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
         <v>2.55</v>
       </c>
       <c r="U33">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.06</v>
@@ -5721,19 +5721,19 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
         <v>2.85</v>
       </c>
       <c r="AA33">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
         <v>1.64</v>
       </c>
       <c r="AC33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
         <v>1.22</v>
@@ -5742,7 +5742,7 @@
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
         <v>1.81</v>
@@ -5854,7 +5854,7 @@
         <v>1.22</v>
       </c>
       <c r="O34">
-        <v>4.79</v>
+        <v>5.15</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -5863,16 +5863,16 @@
         <v>1.67</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="U34">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5887,22 +5887,22 @@
         <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="AA34">
         <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
         <v>2.2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK34">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -644,16 +644,16 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
         <v>2.99</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK2">
         <v>1.6</v>
@@ -1127,13 +1127,13 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
         <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
         <v>2.88</v>
@@ -1148,7 +1148,7 @@
         <v>2.03</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
         <v>1.15</v>
@@ -1157,10 +1157,10 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>5.65</v>
       </c>
       <c r="AA5">
         <v>1.36</v>
@@ -1175,10 +1175,10 @@
         <v>1.71</v>
       </c>
       <c r="AE5">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
         <v>1.97</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>3.8</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
         <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB7">
         <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
+        <v>3.4</v>
+      </c>
+      <c r="P11">
+        <v>2.15</v>
+      </c>
+      <c r="Q11">
         <v>3.5</v>
       </c>
-      <c r="P11">
-        <v>2.14</v>
-      </c>
-      <c r="Q11">
+      <c r="R11">
+        <v>2.18</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.25</v>
       </c>
-      <c r="R11">
-        <v>2.35</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
         <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AB11">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AG11">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O12">
         <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
         <v>2.18</v>
@@ -2292,37 +2292,37 @@
         <v>1.52</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AA12">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE12">
         <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
         <v>2.08</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P13">
-        <v>6.55</v>
+        <v>7.4</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R13">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA13">
         <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>4.25</v>
+        <v>5.05</v>
       </c>
       <c r="R14">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T14">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U14">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AK14">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,25 +2757,25 @@
         <v>3</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
         <v>1.4</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AA15">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
         <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2932,49 +2932,49 @@
         <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>4.91</v>
       </c>
       <c r="AA16">
         <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AC16">
         <v>2.45</v>
       </c>
       <c r="AD16">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE16">
         <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG16">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
         <v>3.05</v>
@@ -3095,31 +3095,31 @@
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z17">
         <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AB17">
         <v>1.66</v>
@@ -3153,7 +3153,7 @@
         <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="R18">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="S18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="V18">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="W18">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AC18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD18">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AE18">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK18">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="Q19">
         <v>2.56</v>
@@ -3587,13 +3587,13 @@
         <v>1.28</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U20">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
         <v>1.11</v>
@@ -3605,19 +3605,19 @@
         <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA20">
         <v>1.64</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC20">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AD20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3626,7 +3626,7 @@
         <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q21">
-        <v>6.46</v>
+        <v>5.5</v>
       </c>
       <c r="R21">
         <v>2.5</v>
@@ -3756,7 +3756,7 @@
         <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3765,7 +3765,7 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -3774,13 +3774,13 @@
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>2.93</v>
       </c>
       <c r="AK21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O22">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P22">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3931,28 +3931,28 @@
         <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA22">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB22">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2.11</v>
       </c>
       <c r="AD22">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
         <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
         <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4094,22 +4094,22 @@
         <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB23">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC23">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AD23">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.5</v>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4227,19 +4227,19 @@
         <v>3.88</v>
       </c>
       <c r="P24">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S24">
         <v>1.14</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="U24">
         <v>1.8</v>
@@ -4248,7 +4248,7 @@
         <v>1.93</v>
       </c>
       <c r="W24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4263,22 +4263,22 @@
         <v>1.22</v>
       </c>
       <c r="AB24">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AC24">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD24">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AE24">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AF24">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AG24">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4393,16 +4393,16 @@
         <v>2.75</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="R25">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S25">
         <v>1.29</v>
       </c>
       <c r="T25">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
         <v>2.56</v>
@@ -4411,7 +4411,7 @@
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -4426,22 +4426,22 @@
         <v>1.63</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
         <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
         <v>1.66</v>
@@ -4562,10 +4562,10 @@
         <v>2.43</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U26">
         <v>2.06</v>
@@ -4574,10 +4574,10 @@
         <v>1.58</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.13</v>
@@ -4601,10 +4601,10 @@
         <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4882,28 +4882,28 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.82</v>
+        <v>3.36</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S28">
+        <v>1.4</v>
+      </c>
+      <c r="T28">
+        <v>2.7</v>
+      </c>
+      <c r="U28">
+        <v>2.77</v>
+      </c>
+      <c r="V28">
         <v>1.38</v>
-      </c>
-      <c r="T28">
-        <v>2.69</v>
-      </c>
-      <c r="U28">
-        <v>2.94</v>
-      </c>
-      <c r="V28">
-        <v>1.37</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.3</v>
@@ -4912,10 +4912,10 @@
         <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB28">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
         <v>3.5</v>
@@ -4927,10 +4927,10 @@
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>1.16</v>
       </c>
       <c r="O29">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>11</v>
@@ -5090,7 +5090,7 @@
         <v>1.34</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG29">
         <v>1.95</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P30">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
         <v>2.95</v>
       </c>
       <c r="U30">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC30">
         <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="O31">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
         <v>5.17</v>
       </c>
       <c r="Q31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U31">
         <v>2.91</v>
@@ -5404,7 +5404,7 @@
         <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
         <v>3.14</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,40 +5525,40 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P32">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
-        <v>3.64</v>
+        <v>3.19</v>
       </c>
       <c r="R32">
         <v>1.63</v>
       </c>
       <c r="S32">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="T32">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="U32">
         <v>4.33</v>
       </c>
       <c r="V32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
         <v>1.12</v>
       </c>
       <c r="Y32">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Z32">
         <v>2.06</v>
@@ -5567,10 +5567,10 @@
         <v>3.08</v>
       </c>
       <c r="AB32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC32">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD32">
         <v>1.11</v>
@@ -5579,10 +5579,10 @@
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG32">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK32">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5742,7 +5742,7 @@
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG33">
         <v>1.81</v>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O34">
         <v>5.15</v>
       </c>
       <c r="P34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q34">
         <v>1.67</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
+        <v>1.95</v>
+      </c>
+      <c r="AB8">
         <v>1.85</v>
-      </c>
-      <c r="AB8">
-        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.64</v>
+        <v>2.49</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="O13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q13">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
-        <v>2.51</v>
+        <v>2.26</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>3</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q15">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="R15">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
         <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
         <v>3.24</v>
       </c>
       <c r="AA15">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
         <v>1.87</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD15">
         <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="P33">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="U33">
-        <v>2.91</v>
+        <v>1.67</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="Z33">
-        <v>2.85</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="AB33">
-        <v>1.64</v>
+        <v>3.4</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>1.69</v>
       </c>
       <c r="AD33">
+        <v>2.13</v>
+      </c>
+      <c r="AE33">
+        <v>1.5</v>
+      </c>
+      <c r="AF33">
         <v>1.22</v>
       </c>
-      <c r="AE33">
-        <v>1.04</v>
-      </c>
-      <c r="AF33">
-        <v>1.88</v>
-      </c>
       <c r="AG33">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AK33">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-03 21:00:00</t>
+          <t>2026-08-03 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5809,151 +5809,314 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>1.72</v>
+      </c>
+      <c r="O34">
+        <v>3.35</v>
+      </c>
+      <c r="P34">
+        <v>4.15</v>
+      </c>
+      <c r="Q34">
+        <v>2.36</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>1.4</v>
+      </c>
+      <c r="T34">
+        <v>2.55</v>
+      </c>
+      <c r="U34">
+        <v>2.91</v>
+      </c>
+      <c r="V34">
+        <v>1.33</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>2.85</v>
+      </c>
+      <c r="AA34">
+        <v>2.05</v>
+      </c>
+      <c r="AB34">
+        <v>1.64</v>
+      </c>
+      <c r="AC34">
+        <v>3.5</v>
+      </c>
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
+        <v>1.04</v>
+      </c>
+      <c r="AF34">
+        <v>1.88</v>
+      </c>
+      <c r="AG34">
+        <v>1.81</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.24</v>
+      </c>
+      <c r="AK34">
+        <v>1.7</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Delfin SC</t>
         </is>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N34">
+      <c r="N35">
         <v>1.23</v>
       </c>
-      <c r="O34">
+      <c r="O35">
         <v>5.15</v>
       </c>
-      <c r="P34">
+      <c r="P35">
         <v>11</v>
       </c>
-      <c r="Q34">
+      <c r="Q35">
         <v>1.67</v>
       </c>
-      <c r="R34">
+      <c r="R35">
         <v>2.5</v>
       </c>
-      <c r="S34">
+      <c r="S35">
         <v>1.35</v>
       </c>
-      <c r="T34">
+      <c r="T35">
         <v>3.06</v>
       </c>
-      <c r="U34">
+      <c r="U35">
         <v>2.7</v>
       </c>
-      <c r="V34">
+      <c r="V35">
         <v>1.4</v>
       </c>
-      <c r="W34">
+      <c r="W35">
         <v>1.08</v>
       </c>
-      <c r="X34">
+      <c r="X35">
         <v>1</v>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <v>1.25</v>
       </c>
-      <c r="Z34">
+      <c r="Z35">
         <v>3.57</v>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <v>1.79</v>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <v>1.88</v>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <v>3.04</v>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <v>1.3</v>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <v>1.08</v>
       </c>
-      <c r="AF34">
+      <c r="AF35">
         <v>2.2</v>
       </c>
-      <c r="AG34">
+      <c r="AG35">
         <v>1.58</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.1</v>
       </c>
-      <c r="AK34">
+      <c r="AK35">
         <v>3</v>
       </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-08-03 21:00:00</t>
         </is>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>3.34</v>
+        <v>2.96</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -668,13 +668,13 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
         <v>1.69</v>
@@ -1133,10 +1133,10 @@
         <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
         <v>1.18</v>
@@ -1148,10 +1148,10 @@
         <v>2.03</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1166,7 +1166,7 @@
         <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -1178,10 +1178,10 @@
         <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC14">
         <v>4.1</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
+        <v>2.65</v>
+      </c>
+      <c r="P19">
         <v>3.1</v>
       </c>
-      <c r="P19">
-        <v>3.54</v>
-      </c>
       <c r="Q19">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
         <v>1.8</v>
@@ -3442,28 +3442,28 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R20">
         <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
         <v>3.12</v>
@@ -3596,7 +3596,7 @@
         <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.03</v>
@@ -3608,7 +3608,7 @@
         <v>3.96</v>
       </c>
       <c r="AA20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
         <v>2.17</v>
@@ -3623,7 +3623,7 @@
         <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
         <v>2.3</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>1.4</v>
       </c>
       <c r="Q21">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
         <v>1.23</v>
@@ -3753,10 +3753,10 @@
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3768,28 +3768,28 @@
         <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA21">
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R22">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S22">
         <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V22">
         <v>1.69</v>
@@ -3928,10 +3928,10 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>5.55</v>
+        <v>5.94</v>
       </c>
       <c r="AA22">
         <v>1.43</v>
@@ -3952,7 +3952,7 @@
         <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O25">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="R25">
         <v>2.13</v>
@@ -4402,13 +4402,13 @@
         <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U25">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
         <v>1.11</v>
@@ -4429,16 +4429,16 @@
         <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
         <v>2.15</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
         <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U2">
         <v>2.99</v>
@@ -680,10 +680,10 @@
         <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.6</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q5">
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="S5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T5">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="U5">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W5">
         <v>1.17</v>
@@ -1157,31 +1157,31 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
         <v>2.88</v>
       </c>
       <c r="AC5">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="Q7">
         <v>2.45</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.42</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
         <v>1.38</v>
@@ -1495,7 +1495,7 @@
         <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
         <v>1.24</v>
@@ -1504,7 +1504,7 @@
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG7">
         <v>1.82</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>7.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q10">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.74</v>
+        <v>4.29</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB10">
         <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE10">
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
         <v>2.18</v>
@@ -2135,16 +2135,16 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="AA11">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC11">
         <v>2.74</v>
@@ -2153,13 +2153,13 @@
         <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,31 +2274,31 @@
         <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R12">
         <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
         <v>4.22</v>
@@ -2313,10 +2313,10 @@
         <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
         <v>1.67</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK12">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q13">
         <v>2.24</v>
@@ -2449,13 +2449,13 @@
         <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,22 +2467,22 @@
         <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
         <v>3.28</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
         <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
         <v>1.85</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2624,10 +2624,10 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z14">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="AA14">
         <v>2.33</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
         <v>1.18</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
+        <v>2.95</v>
+      </c>
+      <c r="O15">
         <v>3</v>
       </c>
-      <c r="O15">
-        <v>3.1</v>
-      </c>
       <c r="P15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="R15">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S15">
         <v>1.34</v>
@@ -2781,7 +2781,7 @@
         <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,13 +2790,13 @@
         <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AA15">
         <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
         <v>3.14</v>
@@ -2808,7 +2808,7 @@
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
         <v>2</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R16">
         <v>2.25</v>
@@ -2941,7 +2941,7 @@
         <v>2.25</v>
       </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
         <v>1.13</v>
@@ -2959,22 +2959,22 @@
         <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AC16">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD16">
         <v>1.56</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U17">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3116,7 +3116,7 @@
         <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3125,7 +3125,7 @@
         <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AD17">
         <v>1.19</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
         <v>1.57</v>
@@ -3252,34 +3252,34 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R18">
+        <v>3.28</v>
+      </c>
+      <c r="S18">
+        <v>1.14</v>
+      </c>
+      <c r="T18">
         <v>3.3</v>
       </c>
-      <c r="S18">
-        <v>1.11</v>
-      </c>
-      <c r="T18">
-        <v>5.5</v>
-      </c>
       <c r="U18">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="V18">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W18">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA18">
         <v>1.25</v>
@@ -3288,19 +3288,19 @@
         <v>3.8</v>
       </c>
       <c r="AC18">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AD18">
         <v>2.2</v>
       </c>
       <c r="AE18">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK18">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="O19">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P19">
-        <v>3.1</v>
+        <v>3.57</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3424,7 +3424,7 @@
         <v>1.53</v>
       </c>
       <c r="T19">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="U19">
         <v>2.95</v>
@@ -3433,7 +3433,7 @@
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1.09</v>
@@ -3454,7 +3454,7 @@
         <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,16 +3578,16 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
         <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="U20">
         <v>2.39</v>
@@ -3608,7 +3608,7 @@
         <v>3.96</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB20">
         <v>2.17</v>
@@ -3735,13 +3735,13 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="P21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>6.51</v>
       </c>
       <c r="R21">
         <v>2.51</v>
@@ -3753,7 +3753,7 @@
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V21">
         <v>1.68</v>
@@ -3768,28 +3768,28 @@
         <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA21">
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD21">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG21">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="AK21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>4.7</v>
       </c>
       <c r="P22">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
         <v>1.94</v>
@@ -3922,13 +3922,13 @@
         <v>1.69</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z22">
         <v>5.94</v>
@@ -3949,10 +3949,10 @@
         <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,49 +4058,49 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U23">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="V23">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
         <v>2.55</v>
@@ -4109,13 +4109,13 @@
         <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4242,10 +4242,10 @@
         <v>4.45</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V24">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="W24">
         <v>1.29</v>
@@ -4260,10 +4260,10 @@
         <v>7.5</v>
       </c>
       <c r="AA24">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB24">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AC24">
         <v>1.66</v>
@@ -4272,13 +4272,13 @@
         <v>2.11</v>
       </c>
       <c r="AE24">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4387,34 +4387,34 @@
         <v>2.1</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S25">
         <v>1.29</v>
       </c>
       <c r="T25">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.23</v>
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="S26">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="V26">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,28 +4583,28 @@
         <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
+        <v>1.51</v>
+      </c>
+      <c r="AB26">
+        <v>2.26</v>
+      </c>
+      <c r="AC26">
+        <v>2.33</v>
+      </c>
+      <c r="AD26">
+        <v>1.53</v>
+      </c>
+      <c r="AE26">
+        <v>1.18</v>
+      </c>
+      <c r="AF26">
         <v>1.46</v>
       </c>
-      <c r="AB26">
-        <v>2.38</v>
-      </c>
-      <c r="AC26">
-        <v>2.15</v>
-      </c>
-      <c r="AD26">
-        <v>1.57</v>
-      </c>
-      <c r="AE26">
-        <v>1.22</v>
-      </c>
-      <c r="AF26">
-        <v>1.43</v>
-      </c>
       <c r="AG26">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AK26">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>3.25</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4882,46 +4882,46 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="R28">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
         <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -5048,13 +5048,13 @@
         <v>1.54</v>
       </c>
       <c r="R29">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="S29">
         <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U29">
         <v>1.94</v>
@@ -5072,7 +5072,7 @@
         <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5093,7 +5093,7 @@
         <v>1.78</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK29">
-        <v>3.83</v>
+        <v>4.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q30">
         <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
         <v>1.34</v>
@@ -5223,25 +5223,25 @@
         <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC30">
         <v>2.83</v>
@@ -5250,7 +5250,7 @@
         <v>1.38</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
         <v>1.67</v>
@@ -5365,7 +5365,7 @@
         <v>1.72</v>
       </c>
       <c r="O31">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
         <v>5.17</v>
@@ -5377,13 +5377,13 @@
         <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
         <v>2.8</v>
       </c>
       <c r="U31">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="V31">
         <v>1.36</v>
@@ -5404,7 +5404,7 @@
         <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
         <v>3.14</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,10 +5531,10 @@
         <v>2.5</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q32">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="R32">
         <v>1.63</v>
@@ -5549,13 +5549,13 @@
         <v>4.33</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y32">
         <v>1.65</v>
@@ -5564,7 +5564,7 @@
         <v>2.06</v>
       </c>
       <c r="AA32">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB32">
         <v>1.33</v>
@@ -5579,10 +5579,10 @@
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG32">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
         <v>1.39</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="O33">
-        <v>3.85</v>
+        <v>3.97</v>
       </c>
       <c r="P33">
         <v>2.45</v>
@@ -5730,7 +5730,7 @@
         <v>1.28</v>
       </c>
       <c r="AB33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC33">
         <v>1.69</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
         <v>3.35</v>
       </c>
       <c r="P34">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q34">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R34">
         <v>2.1</v>
@@ -5869,31 +5869,31 @@
         <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U34">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V34">
         <v>1.33</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
         <v>3.5</v>
@@ -5905,10 +5905,10 @@
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="O35">
-        <v>5.15</v>
+        <v>4.79</v>
       </c>
       <c r="P35">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="Q35">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R35">
         <v>2.5</v>
@@ -6032,10 +6032,10 @@
         <v>1.35</v>
       </c>
       <c r="T35">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6047,16 +6047,16 @@
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="AA35">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
         <v>3.04</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AK35">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="Q7">
         <v>2.45</v>
@@ -1471,7 +1471,7 @@
         <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="V7">
         <v>1.38</v>
@@ -1483,7 +1483,7 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
         <v>3.2</v>
@@ -1498,7 +1498,7 @@
         <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O9">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>1.39</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
         <v>8.050000000000001</v>
@@ -1951,46 +1951,46 @@
         <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD10">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
@@ -2111,10 +2111,10 @@
         <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2132,28 +2132,28 @@
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB11">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD11">
         <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>1.49</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
         <v>1.29</v>
@@ -2295,13 +2295,13 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
         <v>1.64</v>
@@ -2310,10 +2310,10 @@
         <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
         <v>1.17</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
         <v>4.4</v>
@@ -2452,37 +2452,37 @@
         <v>2.94</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
         <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
         <v>1.85</v>
@@ -2501,7 +2501,7 @@
         <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
         <v>2.25</v>
@@ -2938,10 +2938,10 @@
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
         <v>1.13</v>
@@ -2968,7 +2968,7 @@
         <v>1.56</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
@@ -3255,22 +3255,22 @@
         <v>1.38</v>
       </c>
       <c r="R18">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="S18">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V18">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,7 +3279,7 @@
         <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>7.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
         <v>1.25</v>
@@ -3288,7 +3288,7 @@
         <v>3.8</v>
       </c>
       <c r="AC18">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AD18">
         <v>2.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.01</v>
       </c>
       <c r="AK18">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O19">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>3.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
       </c>
       <c r="R19">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S19">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
         <v>2.95</v>
@@ -3436,16 +3436,16 @@
         <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
@@ -3454,13 +3454,13 @@
         <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
         <v>1.84</v>
@@ -4882,13 +4882,13 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
         <v>2.04</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
         <v>2.69</v>
@@ -4903,7 +4903,7 @@
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
         <v>1.26</v>
@@ -4912,7 +4912,7 @@
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
         <v>1.75</v>
@@ -4921,7 +4921,7 @@
         <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -5072,7 +5072,7 @@
         <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5090,10 +5090,10 @@
         <v>1.34</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
         <v>3.6</v>
@@ -5214,7 +5214,7 @@
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
         <v>2.95</v>
@@ -5223,19 +5223,19 @@
         <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="AA30">
         <v>1.79</v>
@@ -5253,7 +5253,7 @@
         <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG30">
         <v>2</v>
@@ -5371,16 +5371,16 @@
         <v>5.17</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R31">
         <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U31">
         <v>2.77</v>
@@ -5392,13 +5392,13 @@
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
         <v>2</v>
@@ -5413,10 +5413,10 @@
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG31">
         <v>1.87</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="P32">
         <v>2.95</v>
@@ -5555,7 +5555,7 @@
         <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Y32">
         <v>1.65</v>
@@ -5564,7 +5564,7 @@
         <v>2.06</v>
       </c>
       <c r="AA32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB32">
         <v>1.33</v>
@@ -5573,16 +5573,16 @@
         <v>6.5</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG32">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK32">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
         <v>2.48</v>
@@ -5866,49 +5866,49 @@
         <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U34">
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
         <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
         <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
         <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD34">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O35">
         <v>4.79</v>
@@ -6035,7 +6035,7 @@
         <v>3.04</v>
       </c>
       <c r="U35">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6044,28 +6044,28 @@
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
         <v>3.53</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB35">
         <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
         <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>2.2</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
         <v>3.6</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3116,7 +3116,7 @@
         <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3131,13 +3131,13 @@
         <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
         <v>1.57</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
         <v>2.48</v>
@@ -5875,40 +5875,40 @@
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA34">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AB34">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC34">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>1.25</v>
       </c>
       <c r="O35">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>10.3</v>
@@ -6035,16 +6035,16 @@
         <v>3.04</v>
       </c>
       <c r="U35">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.25</v>
@@ -6053,25 +6053,25 @@
         <v>3.53</v>
       </c>
       <c r="AA35">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
         <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG35">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AK35">
         <v>3.6</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3252,25 +3252,25 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R18">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="S18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V18">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,7 +3279,7 @@
         <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>4.33</v>
+        <v>8.1</v>
       </c>
       <c r="AA18">
         <v>1.25</v>
@@ -3288,16 +3288,16 @@
         <v>3.8</v>
       </c>
       <c r="AC18">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AD18">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
         <v>2.1</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK18">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3433,16 +3433,16 @@
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
         <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
@@ -5374,22 +5374,22 @@
         <v>2.32</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="U31">
         <v>2.77</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5404,22 +5404,22 @@
         <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC31">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL31">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O2">
         <v>3.1</v>
@@ -644,7 +644,7 @@
         <v>3.2</v>
       </c>
       <c r="Q2">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R2">
         <v>1.97</v>
@@ -653,7 +653,7 @@
         <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="U2">
         <v>2.99</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="AA2">
         <v>2.15</v>
@@ -683,7 +683,7 @@
         <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -692,7 +692,7 @@
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
         <v>1.6</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
         <v>8.050000000000001</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="S5">
         <v>1.19</v>
       </c>
       <c r="T5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
         <v>2.05</v>
       </c>
       <c r="V5">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
         <v>1.17</v>
@@ -1160,7 +1160,7 @@
         <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA5">
         <v>1.37</v>
@@ -1175,7 +1175,7 @@
         <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF5">
         <v>1.69</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK5">
         <v>3.28</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1471,7 +1471,7 @@
         <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
         <v>1.38</v>
@@ -1498,7 +1498,7 @@
         <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
         <v>1.89</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O10">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>8.050000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
         <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
         <v>1.29</v>
@@ -1969,28 +1969,28 @@
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA10">
         <v>1.67</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
@@ -2105,10 +2105,10 @@
         <v>2.8</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
         <v>3.4</v>
@@ -2138,13 +2138,13 @@
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA11">
         <v>1.73</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
         <v>2.8</v>
@@ -2153,7 +2153,7 @@
         <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
         <v>1.49</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O12">
         <v>3.7</v>
@@ -2289,16 +2289,16 @@
         <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
         <v>4.2</v>
@@ -2310,13 +2310,13 @@
         <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
         <v>1.67</v>
@@ -2431,7 +2431,7 @@
         <v>1.67</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
         <v>4.4</v>
@@ -2449,40 +2449,40 @@
         <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
         <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB13">
         <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
         <v>1.85</v>
@@ -2501,7 +2501,7 @@
         <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,13 +2600,13 @@
         <v>2.34</v>
       </c>
       <c r="Q14">
-        <v>5.05</v>
+        <v>4.93</v>
       </c>
       <c r="R14">
         <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
         <v>2.36</v>
@@ -2624,22 +2624,22 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AA14">
         <v>2.33</v>
       </c>
       <c r="AB14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
         <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2664,7 +2664,7 @@
         <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,25 +2763,25 @@
         <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="R15">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
         <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2796,19 +2796,19 @@
         <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG15">
         <v>2</v>
@@ -2926,19 +2926,19 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R16">
         <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
         <v>1.55</v>
@@ -2956,7 +2956,7 @@
         <v>4.91</v>
       </c>
       <c r="AA16">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB16">
         <v>2.39</v>
@@ -2965,7 +2965,7 @@
         <v>2.5</v>
       </c>
       <c r="AD16">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
         <v>1.17</v>
@@ -3092,7 +3092,7 @@
         <v>2.83</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3116,7 +3116,7 @@
         <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3131,7 +3131,7 @@
         <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
         <v>1.57</v>
@@ -3252,10 +3252,10 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R18">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="S18">
         <v>1.1</v>
@@ -3279,22 +3279,22 @@
         <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB18">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AC18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD18">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE18">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF18">
         <v>1.73</v>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="AK18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P19">
         <v>3.8</v>
@@ -3578,22 +3578,22 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R20">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="U20">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,31 +3602,31 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
         <v>3.96</v>
       </c>
       <c r="AA20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
         <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q21">
-        <v>6.51</v>
+        <v>6.56</v>
       </c>
       <c r="R21">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
         <v>3.9</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
         <v>1.68</v>
@@ -3777,7 +3777,7 @@
         <v>2.63</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
         <v>1.67</v>
@@ -3786,10 +3786,10 @@
         <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG21">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>3.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
         <v>1.1</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O22">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
         <v>1.94</v>
       </c>
       <c r="R22">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
         <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3928,7 +3928,7 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
         <v>5.94</v>
@@ -3937,7 +3937,7 @@
         <v>1.43</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC22">
         <v>2.11</v>
@@ -3946,13 +3946,13 @@
         <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4064,19 +4064,19 @@
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
         <v>2.29</v>
@@ -4085,7 +4085,7 @@
         <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4094,28 +4094,28 @@
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="AA23">
         <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC23">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
         <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="S24">
         <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="W24">
         <v>1.29</v>
@@ -4257,7 +4257,7 @@
         <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA24">
         <v>1.24</v>
@@ -4266,10 +4266,10 @@
         <v>3.34</v>
       </c>
       <c r="AC24">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD24">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AE24">
         <v>1.47</v>
@@ -4278,7 +4278,7 @@
         <v>1.25</v>
       </c>
       <c r="AG24">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>2.1</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
         <v>3.2</v>
@@ -4396,25 +4396,25 @@
         <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.23</v>
@@ -4432,13 +4432,13 @@
         <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
         <v>2.15</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK25">
         <v>1.62</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="R26">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.24</v>
+        <v>2.53</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="AD26">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,43 +4710,43 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P27">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA27">
         <v>2.15</v>
@@ -4755,19 +4755,19 @@
         <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,37 +4882,37 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R28">
         <v>2.04</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
         <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
         <v>1.75</v>
@@ -4921,7 +4921,7 @@
         <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -4946,7 +4946,7 @@
         <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,25 +5042,25 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S29">
         <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U29">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W29">
         <v>1.2</v>
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z29">
-        <v>6.84</v>
+        <v>6.72</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5087,10 +5087,10 @@
         <v>1.87</v>
       </c>
       <c r="AE29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG29">
         <v>1.95</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="Q30">
         <v>2.33</v>
@@ -5214,7 +5214,7 @@
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
         <v>2.95</v>
@@ -5226,16 +5226,16 @@
         <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
         <v>1.79</v>
@@ -5247,16 +5247,16 @@
         <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
         <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>5.17</v>
       </c>
       <c r="Q31">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
         <v>2.1</v>
@@ -5380,10 +5380,10 @@
         <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="U31">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
         <v>1.31</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="O32">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="P32">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q32">
-        <v>3.66</v>
+        <v>3.45</v>
       </c>
       <c r="R32">
         <v>1.63</v>
       </c>
       <c r="S32">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T32">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U32">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="V32">
         <v>1.14</v>
@@ -5579,7 +5579,7 @@
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG32">
         <v>1.53</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK32">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5730,7 +5730,7 @@
         <v>1.28</v>
       </c>
       <c r="AB33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC33">
         <v>1.69</v>
@@ -5884,7 +5884,7 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
         <v>2.85</v>
@@ -5896,16 +5896,16 @@
         <v>1.71</v>
       </c>
       <c r="AC34">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
         <v>1.82</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U7">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>4.97</v>
       </c>
       <c r="AA7">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC7">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AD7">
+        <v>1.53</v>
+      </c>
+      <c r="AE7">
+        <v>1.17</v>
+      </c>
+      <c r="AF7">
+        <v>1.5</v>
+      </c>
+      <c r="AG7">
+        <v>2.33</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.21</v>
+      </c>
+      <c r="AK7">
         <v>1.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.06</v>
-      </c>
-      <c r="AF7">
-        <v>1.87</v>
-      </c>
-      <c r="AG7">
-        <v>1.82</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.22</v>
-      </c>
-      <c r="AK7">
-        <v>1.89</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-03 12:45:00</t>
+          <t>2026-08-03 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-03 13:00:00</t>
+          <t>2026-08-03 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
         <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
         <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>2.85</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
         <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA12">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AB12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>1.6</v>
+      </c>
+      <c r="O13">
+        <v>3.7</v>
+      </c>
+      <c r="P13">
+        <v>4.2</v>
+      </c>
+      <c r="Q13">
+        <v>2.13</v>
+      </c>
+      <c r="R13">
+        <v>2.3</v>
+      </c>
+      <c r="S13">
+        <v>1.34</v>
+      </c>
+      <c r="T13">
+        <v>3.11</v>
+      </c>
+      <c r="U13">
+        <v>2.38</v>
+      </c>
+      <c r="V13">
+        <v>1.48</v>
+      </c>
+      <c r="W13">
+        <v>1.09</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.2</v>
+      </c>
+      <c r="Z13">
+        <v>4.2</v>
+      </c>
+      <c r="AA13">
+        <v>1.64</v>
+      </c>
+      <c r="AB13">
+        <v>2.12</v>
+      </c>
+      <c r="AC13">
+        <v>2.52</v>
+      </c>
+      <c r="AD13">
+        <v>1.46</v>
+      </c>
+      <c r="AE13">
+        <v>1.16</v>
+      </c>
+      <c r="AF13">
         <v>1.67</v>
       </c>
-      <c r="O13">
-        <v>3.6</v>
-      </c>
-      <c r="P13">
-        <v>4.4</v>
-      </c>
-      <c r="Q13">
-        <v>2.24</v>
-      </c>
-      <c r="R13">
-        <v>2.26</v>
-      </c>
-      <c r="S13">
-        <v>1.36</v>
-      </c>
-      <c r="T13">
-        <v>2.9</v>
-      </c>
-      <c r="U13">
-        <v>2.75</v>
-      </c>
-      <c r="V13">
-        <v>1.38</v>
-      </c>
-      <c r="W13">
-        <v>1.08</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.28</v>
-      </c>
-      <c r="AA13">
-        <v>1.9</v>
-      </c>
-      <c r="AB13">
-        <v>1.8</v>
-      </c>
-      <c r="AC13">
-        <v>3.28</v>
-      </c>
-      <c r="AD13">
-        <v>1.33</v>
-      </c>
-      <c r="AE13">
-        <v>1.05</v>
-      </c>
-      <c r="AF13">
-        <v>1.83</v>
-      </c>
       <c r="AG13">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.26</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="Q14">
-        <v>4.93</v>
+        <v>2.24</v>
       </c>
       <c r="R14">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="U14">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AA14">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-08-03 13:30:00</t>
+          <t>2026-08-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,65 +2754,65 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>3.78</v>
+        <v>4.93</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="V15">
+        <v>1.28</v>
+      </c>
+      <c r="W15">
+        <v>1.02</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
         <v>1.4</v>
       </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.25</v>
-      </c>
       <c r="Z15">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
+        <v>2.05</v>
+      </c>
+      <c r="AG15">
         <v>1.69</v>
       </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK15">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>4.91</v>
+        <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AG16">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.28</v>
@@ -3270,7 +3270,7 @@
         <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,7 +3279,7 @@
         <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA18">
         <v>1.22</v>
@@ -3297,10 +3297,10 @@
         <v>1.53</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -5392,13 +5392,13 @@
         <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA31">
         <v>2</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
         <v>3.1</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
         <v>2.15</v>
@@ -2763,22 +2763,22 @@
         <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="R15">
         <v>1.93</v>
       </c>
       <c r="S15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U15">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -2787,31 +2787,31 @@
         <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z15">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA15">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG15">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AK15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -4399,28 +4399,28 @@
         <v>2.35</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
         <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
         <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AA25">
         <v>1.63</v>
@@ -4441,7 +4441,7 @@
         <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -638,7 +638,7 @@
         <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
         <v>3.2</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,55 +1127,55 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P5">
-        <v>8.050000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="S5">
         <v>1.19</v>
       </c>
       <c r="T5">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AD5">
         <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
         <v>1.69</v>
@@ -1197,7 +1197,7 @@
         <v>1.01</v>
       </c>
       <c r="AK5">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>1.93</v>
       </c>
       <c r="S15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T15">
         <v>2.54</v>
@@ -2781,7 +2781,7 @@
         <v>1.27</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
         <v>1.05</v>
@@ -2796,7 +2796,7 @@
         <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AC15">
         <v>4.2</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="AK15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3113,10 +3113,10 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3134,10 +3134,10 @@
         <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
         <v>1.57</v>
@@ -3409,10 +3409,10 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3439,7 +3439,7 @@
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
         <v>2.83</v>
@@ -3457,10 +3457,10 @@
         <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
         <v>1.84</v>
@@ -3578,13 +3578,13 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="R20">
         <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T20">
         <v>3.12</v>
@@ -3599,7 +3599,7 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.18</v>
@@ -3608,19 +3608,19 @@
         <v>3.96</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB20">
         <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD20">
         <v>1.4</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.53</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>2.54</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
         <v>3.9</v>
@@ -3756,7 +3756,7 @@
         <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3774,13 +3774,13 @@
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>2.98</v>
       </c>
       <c r="AK21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,10 +3901,10 @@
         <v>4.33</v>
       </c>
       <c r="P22">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R22">
         <v>2.63</v>
@@ -3916,7 +3916,7 @@
         <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="V22">
         <v>1.67</v>
@@ -3931,13 +3931,13 @@
         <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>5.94</v>
+        <v>5.6</v>
       </c>
       <c r="AA22">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB22">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AC22">
         <v>2.11</v>
@@ -3968,7 +3968,7 @@
         <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q23">
         <v>2.5</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U23">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
         <v>1.11</v>
@@ -4094,19 +4094,19 @@
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="AA23">
         <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
         <v>1.2</v>
@@ -4233,19 +4233,19 @@
         <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="S24">
         <v>1.14</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V24">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W24">
         <v>1.29</v>
@@ -4254,22 +4254,22 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z24">
         <v>8.5</v>
       </c>
       <c r="AA24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB24">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AC24">
         <v>1.65</v>
       </c>
       <c r="AD24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE24">
         <v>1.47</v>
@@ -4278,7 +4278,7 @@
         <v>1.25</v>
       </c>
       <c r="AG24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>4.2</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V29">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,7 +5072,7 @@
         <v>1.08</v>
       </c>
       <c r="Z29">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK29">
         <v>4.2</v>
@@ -5697,7 +5697,7 @@
         <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="R33">
         <v>2.57</v>
@@ -5709,7 +5709,7 @@
         <v>4.4</v>
       </c>
       <c r="U33">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V33">
         <v>1.92</v>
@@ -5727,22 +5727,22 @@
         <v>7</v>
       </c>
       <c r="AA33">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB33">
         <v>3.4</v>
       </c>
       <c r="AC33">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AD33">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AE33">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG33">
         <v>3.4</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AK33">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
         <v>1.97</v>
@@ -653,7 +653,7 @@
         <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U2">
         <v>2.99</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.6</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,22 +970,22 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
         <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="U4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -1000,25 +1000,25 @@
         <v>3.59</v>
       </c>
       <c r="AA4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC4">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1127,16 +1127,16 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>8.85</v>
       </c>
       <c r="Q5">
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S5">
         <v>1.19</v>
@@ -1157,7 +1157,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
         <v>6.5</v>
@@ -1172,16 +1172,16 @@
         <v>1.97</v>
       </c>
       <c r="AD5">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE5">
         <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="U6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AD6">
         <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.03</v>
@@ -1501,13 +1501,13 @@
         <v>1.53</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
         <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1619,13 +1619,13 @@
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="Q8">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.42</v>
@@ -1643,7 +1643,7 @@
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
         <v>1.33</v>
@@ -1661,7 +1661,7 @@
         <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
         <v>1.95</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
+        <v>2.76</v>
+      </c>
+      <c r="Q10">
+        <v>2.9</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.37</v>
+      </c>
+      <c r="T10">
+        <v>2.74</v>
+      </c>
+      <c r="U10">
         <v>2.7</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>1.4</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>6.5</v>
@@ -2117,49 +2117,49 @@
         <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
         <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
         <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
         <v>1.14</v>
       </c>
       <c r="AF11">
+        <v>1.84</v>
+      </c>
+      <c r="AG11">
         <v>1.85</v>
-      </c>
-      <c r="AG11">
-        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.2</v>
@@ -2277,7 +2277,7 @@
         <v>3.4</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2295,25 +2295,25 @@
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC12">
         <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.17</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
         <v>1.29</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q13">
         <v>2.13</v>
@@ -2449,7 +2449,7 @@
         <v>3.11</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="V13">
         <v>1.48</v>
@@ -2467,7 +2467,7 @@
         <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
         <v>2.12</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R14">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
         <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,25 +2624,25 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA14">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.83</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>3.11</v>
       </c>
       <c r="P15">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
         <v>4.9</v>
@@ -2790,13 +2790,13 @@
         <v>1.41</v>
       </c>
       <c r="Z15">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="AA15">
         <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC15">
         <v>4.2</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>3</v>
       </c>
       <c r="P16">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="U16">
         <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2950,25 +2950,25 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
         <v>1.69</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,16 +3083,16 @@
         <v>2.2</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q17">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3116,7 +3116,7 @@
         <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3134,10 +3134,10 @@
         <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3255,19 +3255,19 @@
         <v>1.37</v>
       </c>
       <c r="R18">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="S18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="U18">
         <v>1.73</v>
       </c>
       <c r="V18">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="W18">
         <v>1.25</v>
@@ -3276,7 +3276,7 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18">
         <v>7.9</v>
@@ -3288,16 +3288,16 @@
         <v>4.1</v>
       </c>
       <c r="AC18">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD18">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE18">
         <v>1.53</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
         <v>1.6</v>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="AK18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
@@ -3578,7 +3578,7 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="R20">
         <v>2.3</v>
@@ -3587,7 +3587,7 @@
         <v>1.28</v>
       </c>
       <c r="T20">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U20">
         <v>2.4</v>
@@ -3605,7 +3605,7 @@
         <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AA20">
         <v>1.64</v>
@@ -3617,7 +3617,7 @@
         <v>2.75</v>
       </c>
       <c r="AD20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3741,13 +3741,13 @@
         <v>1.35</v>
       </c>
       <c r="Q21">
-        <v>6.56</v>
+        <v>6.61</v>
       </c>
       <c r="R21">
         <v>2.54</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
         <v>3.9</v>
@@ -3771,7 +3771,7 @@
         <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB21">
         <v>2.57</v>
@@ -3780,7 +3780,7 @@
         <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AE21">
         <v>1.29</v>
@@ -3907,22 +3907,22 @@
         <v>1.83</v>
       </c>
       <c r="R22">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S22">
         <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
         <v>2.13</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,28 +3931,28 @@
         <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD22">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
         <v>1.58</v>
       </c>
       <c r="AG22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O25">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
         <v>3</v>
@@ -4432,7 +4432,7 @@
         <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
@@ -4441,7 +4441,7 @@
         <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q26">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="R26">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,49 +4713,49 @@
         <v>1.85</v>
       </c>
       <c r="O27">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q27">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
         <v>1.95</v>
       </c>
       <c r="S27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
         <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AD27">
         <v>1.2</v>
@@ -4764,7 +4764,7 @@
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
         <v>1.83</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4897,7 +4897,7 @@
         <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4921,7 +4921,7 @@
         <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -4930,7 +4930,7 @@
         <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R29">
         <v>3.1</v>
@@ -5069,7 +5069,7 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
         <v>6.66</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>4.38</v>
+        <v>4.05</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="R30">
         <v>2.25</v>
@@ -5235,13 +5235,13 @@
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB30">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>2.83</v>
@@ -5256,7 +5256,7 @@
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5389,16 +5389,16 @@
         <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z31">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="AA31">
         <v>2</v>
@@ -5407,19 +5407,19 @@
         <v>1.75</v>
       </c>
       <c r="AC31">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
         <v>2.5</v>
       </c>
       <c r="P32">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="R32">
         <v>1.63</v>
@@ -5543,10 +5543,10 @@
         <v>1.62</v>
       </c>
       <c r="T32">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U32">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="V32">
         <v>1.14</v>
@@ -5561,10 +5561,10 @@
         <v>1.65</v>
       </c>
       <c r="Z32">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AA32">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AB32">
         <v>1.33</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK32">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5703,16 +5703,16 @@
         <v>2.57</v>
       </c>
       <c r="S33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T33">
         <v>4.4</v>
       </c>
       <c r="U33">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V33">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="W33">
         <v>1.25</v>
@@ -5730,7 +5730,7 @@
         <v>1.3</v>
       </c>
       <c r="AB33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC33">
         <v>1.74</v>
@@ -5742,7 +5742,7 @@
         <v>1.48</v>
       </c>
       <c r="AF33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG33">
         <v>3.4</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
         <v>1.57</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
         <v>3.6</v>
@@ -5863,13 +5863,13 @@
         <v>2.48</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U34">
         <v>3</v>
@@ -5881,34 +5881,34 @@
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB34">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC34">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD34">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O35">
         <v>5</v>
@@ -6023,25 +6023,25 @@
         <v>10.3</v>
       </c>
       <c r="Q35">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
         <v>2.5</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U35">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6050,28 +6050,28 @@
         <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="AA35">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.21</v>
+        <v>2.97</v>
       </c>
       <c r="AD35">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AG35">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="AK35">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.74</v>
+        <v>4.09</v>
       </c>
       <c r="Q8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
         <v>2.15</v>
@@ -1643,7 +1643,7 @@
         <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.33</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>2.76</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U10">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
+        <v>1.67</v>
+      </c>
+      <c r="AB10">
+        <v>1.88</v>
+      </c>
+      <c r="AC10">
+        <v>2.88</v>
+      </c>
+      <c r="AD10">
+        <v>1.33</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>1.84</v>
+      </c>
+      <c r="AG10">
         <v>1.85</v>
       </c>
-      <c r="AB10">
-        <v>1.85</v>
-      </c>
-      <c r="AC10">
-        <v>2.9</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.1</v>
-      </c>
-      <c r="AF10">
-        <v>1.67</v>
-      </c>
-      <c r="AG10">
-        <v>2.1</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.47</v>
+        <v>2.85</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.84</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AK11">
-        <v>2.85</v>
+        <v>1.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>2.13</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="U12">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AK12">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q13">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA13">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
+        <v>1.83</v>
+      </c>
+      <c r="AC13">
+        <v>3.3</v>
+      </c>
+      <c r="AD13">
+        <v>1.31</v>
+      </c>
+      <c r="AE13">
+        <v>1.06</v>
+      </c>
+      <c r="AF13">
+        <v>1.83</v>
+      </c>
+      <c r="AG13">
+        <v>1.85</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.19</v>
+      </c>
+      <c r="AK13">
         <v>2.12</v>
-      </c>
-      <c r="AC13">
-        <v>2.52</v>
-      </c>
-      <c r="AD13">
-        <v>1.46</v>
-      </c>
-      <c r="AE13">
-        <v>1.16</v>
-      </c>
-      <c r="AF13">
-        <v>1.67</v>
-      </c>
-      <c r="AG13">
-        <v>2.05</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.13</v>
-      </c>
-      <c r="AK13">
-        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="O14">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q14">
-        <v>2.16</v>
+        <v>2.9</v>
       </c>
       <c r="R14">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q17">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3116,7 +3116,7 @@
         <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
         <v>2.09</v>
@@ -3134,10 +3134,10 @@
         <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3255,19 +3255,19 @@
         <v>1.37</v>
       </c>
       <c r="R18">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T18">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="W18">
         <v>1.25</v>
@@ -3288,19 +3288,19 @@
         <v>4.1</v>
       </c>
       <c r="AC18">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD18">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG18">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="AK18">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P19">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3439,10 +3439,10 @@
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
@@ -3454,7 +3454,7 @@
         <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
         <v>1.07</v>
@@ -3463,7 +3463,7 @@
         <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4722,37 +4722,37 @@
         <v>2.38</v>
       </c>
       <c r="R27">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="V27">
         <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="AA27">
         <v>2.08</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
         <v>4</v>
@@ -4897,7 +4897,7 @@
         <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4906,16 +4906,16 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
         <v>3.4</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -5229,13 +5229,13 @@
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA30">
         <v>1.78</v>
@@ -5368,7 +5368,7 @@
         <v>3.35</v>
       </c>
       <c r="P31">
-        <v>5.17</v>
+        <v>4.53</v>
       </c>
       <c r="Q31">
         <v>2.3</v>
@@ -5377,16 +5377,16 @@
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.22</v>
+        <v>2.73</v>
       </c>
       <c r="U31">
         <v>2.78</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
         <v>1.05</v>
@@ -5395,10 +5395,10 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA31">
         <v>2</v>
@@ -5407,7 +5407,7 @@
         <v>1.75</v>
       </c>
       <c r="AC31">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="O32">
         <v>2.5</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="Q32">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R32">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S32">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U32">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="V32">
         <v>1.14</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
         <v>1.18</v>
@@ -5561,13 +5561,13 @@
         <v>1.65</v>
       </c>
       <c r="Z32">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AA32">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AB32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC32">
         <v>6.5</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
         <v>3.25</v>
@@ -5866,10 +5866,10 @@
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U34">
         <v>3</v>
@@ -5878,7 +5878,7 @@
         <v>1.33</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5890,10 +5890,10 @@
         <v>3.1</v>
       </c>
       <c r="AA34">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB34">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
         <v>3.42</v>
@@ -5924,7 +5924,7 @@
         <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,43 +6014,43 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="Q35">
         <v>1.75</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
         <v>1.95</v>
@@ -6059,13 +6059,13 @@
         <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>2.33</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>2.13</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC11">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AK11">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O12">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q12">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
+        <v>1.83</v>
+      </c>
+      <c r="AC12">
+        <v>3.3</v>
+      </c>
+      <c r="AD12">
+        <v>1.31</v>
+      </c>
+      <c r="AE12">
+        <v>1.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.83</v>
+      </c>
+      <c r="AG12">
+        <v>1.85</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.19</v>
+      </c>
+      <c r="AK12">
         <v>2.12</v>
-      </c>
-      <c r="AC12">
-        <v>2.52</v>
-      </c>
-      <c r="AD12">
-        <v>1.46</v>
-      </c>
-      <c r="AE12">
-        <v>1.16</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.13</v>
-      </c>
-      <c r="AK12">
-        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
+        <v>3.4</v>
+      </c>
+      <c r="P14">
+        <v>2.2</v>
+      </c>
+      <c r="Q14">
+        <v>3.4</v>
+      </c>
+      <c r="R14">
+        <v>2.25</v>
+      </c>
+      <c r="S14">
+        <v>1.3</v>
+      </c>
+      <c r="T14">
         <v>3.25</v>
       </c>
-      <c r="P14">
-        <v>2.76</v>
-      </c>
-      <c r="Q14">
-        <v>2.9</v>
-      </c>
-      <c r="R14">
-        <v>2.2</v>
-      </c>
-      <c r="S14">
-        <v>1.37</v>
-      </c>
-      <c r="T14">
-        <v>2.74</v>
-      </c>
       <c r="U14">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC14">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD14">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK14">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
         <v>2.48</v>
@@ -5866,19 +5866,19 @@
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,22 +5887,22 @@
         <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA34">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC34">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD34">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,13 +6017,13 @@
         <v>1.19</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4.94</v>
       </c>
       <c r="P35">
         <v>11.1</v>
       </c>
       <c r="Q35">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R35">
         <v>2.4</v>
@@ -6041,7 +6041,7 @@
         <v>1.35</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.04</v>
@@ -6050,7 +6050,7 @@
         <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="AA35">
         <v>1.95</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
         <v>3.4</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="Q2">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="R2">
         <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.03</v>
@@ -668,19 +668,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
         <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.58</v>
+        <v>4.03</v>
       </c>
       <c r="AD2">
         <v>1.21</v>
@@ -689,11 +689,11 @@
         <v>1.04</v>
       </c>
       <c r="AF2">
+        <v>1.85</v>
+      </c>
+      <c r="AG2">
         <v>1.83</v>
       </c>
-      <c r="AG2">
-        <v>1.85</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
+        <v>2.69</v>
+      </c>
+      <c r="U8">
         <v>2.88</v>
       </c>
-      <c r="U8">
-        <v>2.74</v>
-      </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.04</v>
@@ -1649,7 +1649,7 @@
         <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
         <v>2.04</v>
@@ -1658,19 +1658,19 @@
         <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P9">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1942,61 +1942,61 @@
         <v>1.4</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q10">
         <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U10">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB10">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK10">
         <v>2.85</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
         <v>4.33</v>
@@ -2114,7 +2114,7 @@
         <v>2.13</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S11">
         <v>1.34</v>
@@ -2123,43 +2123,43 @@
         <v>3.11</v>
       </c>
       <c r="U11">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA11">
         <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
         <v>4.6</v>
       </c>
       <c r="Q12">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R12">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
+        <v>3.4</v>
+      </c>
+      <c r="P13">
+        <v>2.2</v>
+      </c>
+      <c r="Q13">
+        <v>3.09</v>
+      </c>
+      <c r="R13">
+        <v>2.15</v>
+      </c>
+      <c r="S13">
+        <v>1.3</v>
+      </c>
+      <c r="T13">
         <v>3.25</v>
       </c>
-      <c r="P13">
-        <v>2.76</v>
-      </c>
-      <c r="Q13">
-        <v>2.9</v>
-      </c>
-      <c r="R13">
-        <v>2.2</v>
-      </c>
-      <c r="S13">
+      <c r="U13">
+        <v>2.45</v>
+      </c>
+      <c r="V13">
+        <v>1.5</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>1.21</v>
+      </c>
+      <c r="Z13">
+        <v>4.33</v>
+      </c>
+      <c r="AA13">
+        <v>1.68</v>
+      </c>
+      <c r="AB13">
+        <v>2.11</v>
+      </c>
+      <c r="AC13">
+        <v>2.75</v>
+      </c>
+      <c r="AD13">
         <v>1.37</v>
       </c>
-      <c r="T13">
-        <v>2.74</v>
-      </c>
-      <c r="U13">
-        <v>2.7</v>
-      </c>
-      <c r="V13">
-        <v>1.38</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>1.27</v>
-      </c>
-      <c r="Z13">
-        <v>3.4</v>
-      </c>
-      <c r="AA13">
-        <v>1.85</v>
-      </c>
-      <c r="AB13">
-        <v>1.85</v>
-      </c>
-      <c r="AC13">
-        <v>2.9</v>
-      </c>
-      <c r="AD13">
-        <v>1.32</v>
-      </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AK13">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.25</v>
+      </c>
+      <c r="O14">
+        <v>3.12</v>
+      </c>
+      <c r="P14">
+        <v>2.89</v>
+      </c>
+      <c r="Q14">
+        <v>2.9</v>
+      </c>
+      <c r="R14">
+        <v>2.2</v>
+      </c>
+      <c r="S14">
+        <v>1.35</v>
+      </c>
+      <c r="T14">
+        <v>3.07</v>
+      </c>
+      <c r="U14">
         <v>2.7</v>
       </c>
-      <c r="O14">
-        <v>3.4</v>
-      </c>
-      <c r="P14">
-        <v>2.2</v>
-      </c>
-      <c r="Q14">
-        <v>3.4</v>
-      </c>
-      <c r="R14">
-        <v>2.25</v>
-      </c>
-      <c r="S14">
-        <v>1.3</v>
-      </c>
-      <c r="T14">
-        <v>3.25</v>
-      </c>
-      <c r="U14">
-        <v>2.45</v>
-      </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB14">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="P15">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q15">
         <v>4.9</v>
       </c>
       <c r="R15">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S15">
         <v>1.51</v>
@@ -2787,19 +2787,19 @@
         <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z15">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="AA15">
         <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AC15">
-        <v>4.2</v>
+        <v>4.58</v>
       </c>
       <c r="AD15">
         <v>1.15</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,28 +2923,28 @@
         <v>3</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="U16">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,13 +2956,13 @@
         <v>3.14</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
         <v>1.27</v>
@@ -2971,10 +2971,10 @@
         <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
         <v>1.41</v>
@@ -3101,10 +3101,10 @@
         <v>2.59</v>
       </c>
       <c r="U17">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3113,7 +3113,7 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z17">
         <v>2.9</v>
@@ -3131,7 +3131,7 @@
         <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3409,19 +3409,19 @@
         <v>2.28</v>
       </c>
       <c r="O19">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P19">
-        <v>2.85</v>
+        <v>3.61</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
       </c>
       <c r="R19">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T19">
         <v>2.65</v>
@@ -3442,7 +3442,7 @@
         <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
@@ -3457,10 +3457,10 @@
         <v>1.26</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
         <v>1.85</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.6</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
         <v>3.35</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.64</v>
+        <v>4.77</v>
       </c>
       <c r="AA23">
         <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC23">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG23">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O27">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.43</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA27">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG27">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,22 +4882,22 @@
         <v>2.81</v>
       </c>
       <c r="Q28">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U28">
         <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4906,31 +4906,31 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB28">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
         <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG28">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
         <v>1.36</v>
@@ -5039,13 +5039,13 @@
         <v>1.16</v>
       </c>
       <c r="O29">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="P29">
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="R29">
         <v>3.1</v>
@@ -5054,16 +5054,16 @@
         <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U29">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V29">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,7 +5072,7 @@
         <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>6.66</v>
+        <v>6.98</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5087,10 +5087,10 @@
         <v>1.87</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
         <v>1.95</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="P30">
-        <v>3.9</v>
+        <v>4.38</v>
       </c>
       <c r="Q30">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -5235,41 +5235,41 @@
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA30">
         <v>1.78</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
+        <v>1.1</v>
+      </c>
+      <c r="AF30">
+        <v>1.77</v>
+      </c>
+      <c r="AG30">
+        <v>1.9</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.11</v>
-      </c>
-      <c r="AF30">
-        <v>1.75</v>
-      </c>
-      <c r="AG30">
-        <v>1.95</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.18</v>
       </c>
       <c r="AK30">
         <v>2.09</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="S3">
         <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
         <v>3.04</v>
@@ -825,7 +825,7 @@
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,7 +834,7 @@
         <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA3">
         <v>2.11</v>
@@ -843,16 +843,16 @@
         <v>1.68</v>
       </c>
       <c r="AC3">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
         <v>1.84</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.7</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB4">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AD4">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>8.85</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S5">
         <v>1.19</v>
       </c>
       <c r="T5">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,22 +1160,22 @@
         <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AC5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD5">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1317,22 +1317,22 @@
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="AD6">
         <v>1.37</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V7">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>5.13</v>
+      </c>
+      <c r="AA7">
+        <v>1.47</v>
+      </c>
+      <c r="AB7">
+        <v>2.35</v>
+      </c>
+      <c r="AC7">
+        <v>2.27</v>
+      </c>
+      <c r="AD7">
+        <v>1.56</v>
+      </c>
+      <c r="AE7">
         <v>1.18</v>
       </c>
-      <c r="Z7">
-        <v>4.97</v>
-      </c>
-      <c r="AA7">
-        <v>1.56</v>
-      </c>
-      <c r="AB7">
-        <v>2.4</v>
-      </c>
-      <c r="AC7">
-        <v>2.5</v>
-      </c>
-      <c r="AD7">
-        <v>1.53</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
         <v>3.5</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>3.09</v>
       </c>
       <c r="R10">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA10">
         <v>1.68</v>
       </c>
       <c r="AB10">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AK10">
-        <v>2.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="P11">
-        <v>4.33</v>
+        <v>7.7</v>
       </c>
       <c r="Q11">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.51</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
         <v>1.11</v>
@@ -2135,31 +2135,31 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB11">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC11">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>2.07</v>
+        <v>2.85</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q12">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="R12">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="S12">
         <v>1.34</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>3.11</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
+        <v>1.41</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.2</v>
+      </c>
+      <c r="Z12">
+        <v>3.95</v>
+      </c>
+      <c r="AA12">
+        <v>1.65</v>
+      </c>
+      <c r="AB12">
+        <v>2.11</v>
+      </c>
+      <c r="AC12">
+        <v>2.56</v>
+      </c>
+      <c r="AD12">
         <v>1.4</v>
       </c>
-      <c r="W12">
-        <v>1.04</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>1.22</v>
-      </c>
-      <c r="Z12">
-        <v>3.5</v>
-      </c>
-      <c r="AA12">
-        <v>1.83</v>
-      </c>
-      <c r="AB12">
-        <v>1.87</v>
-      </c>
-      <c r="AC12">
-        <v>2.63</v>
-      </c>
-      <c r="AD12">
-        <v>1.28</v>
-      </c>
       <c r="AE12">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK12">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>1.58</v>
+      </c>
+      <c r="O13">
+        <v>3.6</v>
+      </c>
+      <c r="P13">
+        <v>4.6</v>
+      </c>
+      <c r="Q13">
+        <v>2.17</v>
+      </c>
+      <c r="R13">
+        <v>2.39</v>
+      </c>
+      <c r="S13">
+        <v>1.34</v>
+      </c>
+      <c r="T13">
+        <v>2.32</v>
+      </c>
+      <c r="U13">
         <v>2.7</v>
       </c>
-      <c r="O13">
-        <v>3.4</v>
-      </c>
-      <c r="P13">
-        <v>2.2</v>
-      </c>
-      <c r="Q13">
-        <v>3.09</v>
-      </c>
-      <c r="R13">
-        <v>2.15</v>
-      </c>
-      <c r="S13">
-        <v>1.3</v>
-      </c>
-      <c r="T13">
-        <v>3.25</v>
-      </c>
-      <c r="U13">
-        <v>2.45</v>
-      </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB13">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD13">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>2.14</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R16">
         <v>1.95</v>
@@ -2935,19 +2935,19 @@
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U16">
         <v>2.79</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.27</v>
@@ -2956,19 +2956,19 @@
         <v>3.14</v>
       </c>
       <c r="AA16">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>1.71</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,25 +3252,25 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R18">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="S18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="U18">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="V18">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,25 +3279,25 @@
         <v>1.02</v>
       </c>
       <c r="Z18">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB18">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC18">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD18">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AE18">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AF18">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
         <v>1.57</v>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="AK18">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="O19">
         <v>2.85</v>
       </c>
       <c r="P19">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3424,40 +3424,40 @@
         <v>1.52</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AD19">
         <v>1.26</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.85</v>
@@ -3578,28 +3578,28 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
         <v>3.14</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.18</v>
@@ -3608,22 +3608,22 @@
         <v>4</v>
       </c>
       <c r="AA20">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB20">
         <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD20">
         <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
         <v>2.25</v>
@@ -3642,7 +3642,7 @@
         <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>7.47</v>
       </c>
       <c r="O21">
         <v>4.6</v>
@@ -3741,7 +3741,7 @@
         <v>1.35</v>
       </c>
       <c r="Q21">
-        <v>6.61</v>
+        <v>6.56</v>
       </c>
       <c r="R21">
         <v>2.54</v>
@@ -3750,10 +3750,10 @@
         <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V21">
         <v>1.7</v>
@@ -3765,7 +3765,7 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
         <v>5.75</v>
@@ -3774,22 +3774,22 @@
         <v>1.39</v>
       </c>
       <c r="AB21">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD21">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF21">
         <v>1.65</v>
       </c>
       <c r="AG21">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>2.98</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O22">
         <v>4.33</v>
@@ -3904,46 +3904,46 @@
         <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R22">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AC22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD22">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE22">
         <v>1.25</v>
@@ -3952,7 +3952,7 @@
         <v>1.58</v>
       </c>
       <c r="AG22">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q24">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R24">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="S24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
         <v>4.75</v>
       </c>
       <c r="U24">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="V24">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z24">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB24">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC24">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD24">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE24">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AF24">
         <v>1.25</v>
       </c>
       <c r="AG24">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,61 +4384,61 @@
         </is>
       </c>
       <c r="N25">
+        <v>2.08</v>
+      </c>
+      <c r="O25">
+        <v>2.98</v>
+      </c>
+      <c r="P25">
+        <v>2.75</v>
+      </c>
+      <c r="Q25">
+        <v>2.78</v>
+      </c>
+      <c r="R25">
         <v>2.12</v>
       </c>
-      <c r="O25">
-        <v>3.45</v>
-      </c>
-      <c r="P25">
-        <v>3</v>
-      </c>
-      <c r="Q25">
-        <v>2.75</v>
-      </c>
-      <c r="R25">
-        <v>2.35</v>
-      </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V25">
         <v>1.44</v>
       </c>
       <c r="W25">
+        <v>1.07</v>
+      </c>
+      <c r="X25">
+        <v>1.03</v>
+      </c>
+      <c r="Y25">
+        <v>1.24</v>
+      </c>
+      <c r="Z25">
+        <v>3.58</v>
+      </c>
+      <c r="AA25">
+        <v>1.77</v>
+      </c>
+      <c r="AB25">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>2.74</v>
+      </c>
+      <c r="AD25">
+        <v>1.35</v>
+      </c>
+      <c r="AE25">
         <v>1.11</v>
       </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.23</v>
-      </c>
-      <c r="Z25">
-        <v>4</v>
-      </c>
-      <c r="AA25">
-        <v>1.63</v>
-      </c>
-      <c r="AB25">
-        <v>2.1</v>
-      </c>
-      <c r="AC25">
-        <v>2.55</v>
-      </c>
-      <c r="AD25">
-        <v>1.36</v>
-      </c>
-      <c r="AE25">
-        <v>1.15</v>
-      </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
         <v>2.15</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
         <v>1.62</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="R26">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB26">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5045,16 +5045,16 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="R29">
         <v>3.1</v>
       </c>
       <c r="S29">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T29">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="U29">
         <v>1.94</v>
@@ -5063,37 +5063,37 @@
         <v>1.81</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z29">
-        <v>6.98</v>
+        <v>7.03</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC29">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD29">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE29">
         <v>1.36</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.07</v>
       </c>
       <c r="AK29">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="P31">
-        <v>4.53</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="U31">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
         <v>1.36</v>
@@ -5392,10 +5392,10 @@
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
         <v>3.1</v>
@@ -5416,7 +5416,7 @@
         <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG31">
         <v>1.8</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="P32">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R32">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S32">
         <v>1.68</v>
@@ -5546,40 +5546,40 @@
         <v>2.08</v>
       </c>
       <c r="U32">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V32">
         <v>1.14</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Y32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z32">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AA32">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB32">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC32">
         <v>6.5</v>
       </c>
       <c r="AD32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AG32">
         <v>1.53</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="O33">
-        <v>3.97</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="S33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U33">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V33">
         <v>1.95</v>
@@ -5721,25 +5721,25 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB33">
         <v>3.5</v>
       </c>
       <c r="AC33">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="AD33">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AE33">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF33">
         <v>1.29</v>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,22 +5851,22 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
         <v>2.7</v>
@@ -5893,13 +5893,13 @@
         <v>1.91</v>
       </c>
       <c r="AB34">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AC34">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
         <v>1.1</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
         <v>1.83</v>
@@ -6017,22 +6017,22 @@
         <v>1.19</v>
       </c>
       <c r="O35">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>11.1</v>
+        <v>8.6</v>
       </c>
       <c r="Q35">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
         <v>1.39</v>
       </c>
       <c r="T35">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U35">
         <v>2.82</v>
@@ -6044,22 +6044,22 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
         <v>1.26</v>
@@ -6087,7 +6087,7 @@
         <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="R2">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
         <v>1.46</v>
@@ -668,19 +668,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="AA2">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="AD2">
         <v>1.21</v>
@@ -692,7 +692,7 @@
         <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q15">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="R15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S15">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T15">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="U15">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
         <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB15">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC15">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="AD15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AG15">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -4058,52 +4058,52 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
         <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.77</v>
+        <v>4.45</v>
       </c>
       <c r="AA23">
         <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AC23">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD23">
         <v>1.54</v>
@@ -4112,10 +4112,10 @@
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,118 +624,118 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U2">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z2">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="AA2">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>4.07</v>
+        <v>4.48</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AK2">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U3">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
         <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,46 +970,46 @@
         <v>3.14</v>
       </c>
       <c r="Q4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
         <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="AA4">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
         <v>1.65</v>
@@ -1120,68 +1120,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O5">
         <v>5.5</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="S5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
         <v>1.17</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC5">
         <v>2</v>
       </c>
       <c r="AD5">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="O6">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="P6">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q6">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA6">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
         <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R7">
         <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
         <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
       <c r="AA7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC7">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD7">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
         <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V8">
         <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
         <v>3.4</v>
       </c>
       <c r="P9">
+        <v>1.98</v>
+      </c>
+      <c r="Q9">
+        <v>4.64</v>
+      </c>
+      <c r="R9">
+        <v>2.16</v>
+      </c>
+      <c r="S9">
+        <v>1.39</v>
+      </c>
+      <c r="T9">
+        <v>2.88</v>
+      </c>
+      <c r="U9">
+        <v>2.67</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.08</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.24</v>
+      </c>
+      <c r="Z9">
+        <v>3.34</v>
+      </c>
+      <c r="AA9">
+        <v>1.93</v>
+      </c>
+      <c r="AB9">
         <v>1.83</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>1.95</v>
-      </c>
-      <c r="AB9">
-        <v>1.85</v>
-      </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P15">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="R15">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S15">
         <v>1.55</v>
@@ -2775,10 +2775,10 @@
         <v>2.33</v>
       </c>
       <c r="U15">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
         <v>1.01</v>
@@ -2793,25 +2793,25 @@
         <v>2.43</v>
       </c>
       <c r="AA15">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AB15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE15">
         <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AK15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,37 +2917,37 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O16">
         <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
+        <v>2.78</v>
+      </c>
+      <c r="U16">
         <v>2.8</v>
       </c>
-      <c r="U16">
-        <v>2.79</v>
-      </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.27</v>
@@ -2956,16 +2956,16 @@
         <v>3.14</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AB16">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AC16">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
         <v>1.04</v>
@@ -2974,7 +2974,7 @@
         <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK16">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,25 +3086,25 @@
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S17">
         <v>1.41</v>
       </c>
       <c r="T17">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
         <v>3.02</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3113,22 +3113,22 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA17">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
@@ -3153,7 +3153,7 @@
         <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,77 +3406,77 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="O19">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P19">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
-        <v>3.86</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
+        <v>1.25</v>
+      </c>
+      <c r="AE19">
+        <v>1.06</v>
+      </c>
+      <c r="AF19">
+        <v>1.77</v>
+      </c>
+      <c r="AG19">
+        <v>1.95</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.26</v>
-      </c>
-      <c r="AE19">
-        <v>1.07</v>
-      </c>
-      <c r="AF19">
-        <v>1.85</v>
-      </c>
-      <c r="AG19">
-        <v>1.85</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.6</v>
@@ -3569,40 +3569,40 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="O20">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="P20">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
         <v>3.14</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
         <v>4</v>
@@ -3611,7 +3611,7 @@
         <v>1.63</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
         <v>2.6</v>
@@ -3620,10 +3620,10 @@
         <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
         <v>2.25</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,58 +3732,58 @@
         </is>
       </c>
       <c r="N21">
-        <v>7.47</v>
+        <v>7.25</v>
       </c>
       <c r="O21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q21">
-        <v>6.56</v>
+        <v>6.98</v>
       </c>
       <c r="R21">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
         <v>1.7</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA21">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AB21">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AC21">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AD21">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF21">
         <v>1.65</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O22">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q22">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T22">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V22">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3934,10 +3934,10 @@
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AB22">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2.11</v>
@@ -3946,7 +3946,7 @@
         <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
         <v>1.58</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O23">
         <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
         <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S23">
         <v>1.28</v>
@@ -4082,40 +4082,40 @@
         <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA23">
         <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="AC23">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="AD23">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG23">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="P24">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q24">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="R24">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="S24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T24">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="U24">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="W24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,28 +4257,28 @@
         <v>1.05</v>
       </c>
       <c r="Z24">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA24">
+        <v>1.2</v>
+      </c>
+      <c r="AB24">
+        <v>4.5</v>
+      </c>
+      <c r="AC24">
+        <v>1.52</v>
+      </c>
+      <c r="AD24">
+        <v>2.35</v>
+      </c>
+      <c r="AE24">
+        <v>1.6</v>
+      </c>
+      <c r="AF24">
         <v>1.22</v>
       </c>
-      <c r="AB24">
-        <v>3.8</v>
-      </c>
-      <c r="AC24">
-        <v>1.57</v>
-      </c>
-      <c r="AD24">
-        <v>2.25</v>
-      </c>
-      <c r="AE24">
-        <v>1.58</v>
-      </c>
-      <c r="AF24">
-        <v>1.25</v>
-      </c>
       <c r="AG24">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="O25">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="P25">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="R25">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U25">
         <v>2.56</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
         <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA25">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC25">
         <v>2.74</v>
       </c>
       <c r="AD25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
         <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>4.11</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="S27">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
         <v>1.07</v>
@@ -4743,31 +4743,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z27">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AA27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB27">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O28">
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U28">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V28">
         <v>1.39</v>
@@ -4903,31 +4903,31 @@
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
         <v>2</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
         <v>1.36</v>
@@ -5048,52 +5048,52 @@
         <v>1.44</v>
       </c>
       <c r="R29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S29">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T29">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U29">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="V29">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="W29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z29">
-        <v>7.03</v>
+        <v>7.06</v>
       </c>
       <c r="AA29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC29">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AD29">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG29">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK29">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="O30">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>4.38</v>
+        <v>5.25</v>
       </c>
       <c r="Q30">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="V30">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="S33">
         <v>1.14</v>
       </c>
       <c r="T33">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="V33">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W33">
         <v>1.25</v>
@@ -5724,28 +5724,28 @@
         <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AB33">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC33">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AD33">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AE33">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AG33">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -790,11 +790,11 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -864,7 +864,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "61"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "21", "45+1", "73", "90+9"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "40"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "74"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "45+4", "90"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1935,23 +1935,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1966,80 +1966,80 @@
         <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB10">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AC10">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG10">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "24"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,22 +2070,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,111 +2098,111 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>2.61</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA11">
         <v>1.68</v>
       </c>
       <c r="AB11">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["16", "28", "42"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>2.85</v>
+        <v>1.58</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,139 +2233,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P12">
-        <v>4.33</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q12">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB12">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "14", "31"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "59"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2417,118 +2417,118 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q13">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA13">
+        <v>1.54</v>
+      </c>
+      <c r="AB13">
+        <v>2.14</v>
+      </c>
+      <c r="AC13">
+        <v>2.4</v>
+      </c>
+      <c r="AD13">
+        <v>1.42</v>
+      </c>
+      <c r="AE13">
+        <v>1.15</v>
+      </c>
+      <c r="AF13">
+        <v>1.67</v>
+      </c>
+      <c r="AG13">
         <v>1.83</v>
       </c>
-      <c r="AB13">
-        <v>1.87</v>
-      </c>
-      <c r="AC13">
-        <v>2.63</v>
-      </c>
-      <c r="AD13">
-        <v>1.28</v>
-      </c>
-      <c r="AE13">
-        <v>1.07</v>
-      </c>
-      <c r="AF13">
-        <v>1.82</v>
-      </c>
-      <c r="AG13">
-        <v>1.84</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "77"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,139 +2559,139 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O14">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>2.89</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
+        <v>1.34</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.6</v>
+      </c>
+      <c r="V14">
+        <v>1.4</v>
+      </c>
+      <c r="W14">
+        <v>1.04</v>
+      </c>
+      <c r="X14">
+        <v>1.05</v>
+      </c>
+      <c r="Y14">
+        <v>1.25</v>
+      </c>
+      <c r="Z14">
+        <v>3.57</v>
+      </c>
+      <c r="AA14">
+        <v>1.83</v>
+      </c>
+      <c r="AB14">
+        <v>1.87</v>
+      </c>
+      <c r="AC14">
+        <v>2.55</v>
+      </c>
+      <c r="AD14">
         <v>1.35</v>
       </c>
-      <c r="T14">
-        <v>3.07</v>
-      </c>
-      <c r="U14">
-        <v>2.7</v>
-      </c>
-      <c r="V14">
-        <v>1.38</v>
-      </c>
-      <c r="W14">
-        <v>1.05</v>
-      </c>
-      <c r="X14">
-        <v>1.04</v>
-      </c>
-      <c r="Y14">
-        <v>1.28</v>
-      </c>
-      <c r="Z14">
-        <v>3.5</v>
-      </c>
-      <c r="AA14">
-        <v>1.88</v>
-      </c>
-      <c r="AB14">
-        <v>1.9</v>
-      </c>
-      <c r="AC14">
-        <v>3.1</v>
-      </c>
-      <c r="AD14">
-        <v>1.33</v>
-      </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["32", "49", "52", "83", "89"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67", "84"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,11 +2909,11 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3232,79 +3232,79 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="O18">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P18">
-        <v>9.050000000000001</v>
+        <v>14</v>
       </c>
       <c r="Q18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R18">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="S18">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T18">
         <v>4.6</v>
       </c>
       <c r="U18">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="V18">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="W18">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB18">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC18">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD18">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AE18">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG18">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "90+4"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3316,34 +3316,34 @@
         <v>1</v>
       </c>
       <c r="AK18">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3558,27 +3558,27 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
         <v>2.3</v>
@@ -3608,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="AA20">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB20">
         <v>2.2</v>
@@ -3617,7 +3617,7 @@
         <v>2.6</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3712,13 +3712,13 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "16"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,14 +4047,14 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "72", "90+4"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "25", "64", "90+2"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4376,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "54", "57"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4702,11 +4702,11 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         <v>1.16</v>
       </c>
       <c r="O29">
-        <v>6.3</v>
+        <v>7.75</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q29">
         <v>1.44</v>
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>7.06</v>
+        <v>7.3</v>
       </c>
       <c r="AA29">
         <v>1.33</v>
@@ -5081,19 +5081,19 @@
         <v>3.25</v>
       </c>
       <c r="AC29">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE29">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF29">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG29">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5365,58 +5365,58 @@
         <v>1.73</v>
       </c>
       <c r="O31">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="U31">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
         <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC31">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
         <v>1.8</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="P32">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="R32">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="S32">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="T32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U32">
         <v>4.5</v>
       </c>
       <c r="V32">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W32">
         <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Y32">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Z32">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AA32">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AB32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC32">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AD32">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AG32">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AK32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.41</v>
       </c>
       <c r="T34">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="U34">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5884,25 +5884,25 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
         <v>3.3</v>
       </c>
       <c r="AA34">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB34">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AC34">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
         <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
@@ -5924,7 +5924,7 @@
         <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="O35">
         <v>4.6</v>
       </c>
       <c r="P35">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>1.75</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
+        <v>1.35</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.66</v>
+      </c>
+      <c r="V35">
         <v>1.39</v>
       </c>
-      <c r="T35">
-        <v>2.94</v>
-      </c>
-      <c r="U35">
-        <v>2.82</v>
-      </c>
-      <c r="V35">
-        <v>1.35</v>
-      </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
         <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
+        <v>1.75</v>
+      </c>
+      <c r="AB35">
         <v>1.85</v>
-      </c>
-      <c r="AB35">
-        <v>1.83</v>
       </c>
       <c r="AC35">
         <v>3.25</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AG35">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
         <v>3.42</v>

--- a/jogos_2026-08-03.xlsx
+++ b/jogos_2026-08-03.xlsx
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3398,11 +3398,11 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "90+4"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "12", "28", "53", "55", "60"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4536,14 +4536,14 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67", "80", "90+5"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5025,14 +5025,14 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "86"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "45+1"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "57", "74"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,130 +5665,130 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
         <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R33">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="S33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U33">
         <v>1.71</v>
       </c>
       <c r="V33">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="W33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA33">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AB33">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC33">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AD33">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AE33">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF33">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AG33">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "80"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "88", "90+4"]</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AK33">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         <v>1.87</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -5887,7 +5887,7 @@
         <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
         <v>1.92</v>
